--- a/untitled folder/HSC_Physics_2nd_Paper_Chapter_04_Magnetic_Effects_of_Current_and_Magnetism.xlsx
+++ b/untitled folder/HSC_Physics_2nd_Paper_Chapter_04_Magnetic_Effects_of_Current_and_Magnetism.xlsx
@@ -1219,11 +1219,6 @@
           <t>একটি সোজা তারের মধ্য দিয়ে $I$ তড়িৎ প্রবাহিত হচ্ছে। তারটি থেকে লম্ব দূরত্ব $d$-তে অবস্থিত একটি বিন্দুতে তারের দুই প্রান্ত যথাক্রমে $\theta_1$ এবং $\theta_2$ কোণ উৎপন্ন করলে বায়ো-সাভার্ট সূত্র থেকে প্রমাণ করো যে $B = \frac{\mu_0 I}{4 \pi d}(\sin \theta_1 + \sin \theta_2)$। অসীম ও অর্ধ-অসীম তারের ক্ষেত্রে এর রূপ কী হবে?</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>তারের লম্ব পাদবিন্দু থেকে $x$ দূরত্বে একটি ক্ষুদ্র অংশ $dx$ বিবেচনা করি। পাদবিন্দু থেকে ঐ বিন্দুর কোণ $\theta$ হলে $x = d \tan \theta \implies dx = d \sec^2 \theta d\theta$ এবং দূরত্ব $r = d \sec \theta$। বায়ো-সাভার্ট সূত্রে: $dB = \frac{\mu_0 I dx \cos \theta}{4\pi r^2} = \frac{\mu_0 I (d \sec^2 \theta d\theta) \cos \theta}{4\pi d^2 \sec^2 \theta} = \frac{\mu_0 I}{4\pi d} \cos \theta d\theta$। $-\theta_1$ থেকে $+\theta_2$ সীমায় সমাকলন করে: $B = \frac{\mu_0 I}{4\pi d} \int_{-\theta_1}^{\theta_2} \cos \theta d\theta = \frac{\mu_0 I}{4\pi d} [\sin \theta]_{-\theta_1}^{\theta_2} = \frac{\mu_0 I}{4\pi d}(\sin \theta_1 + \sin \theta_2)$। অসীম তারের ক্ষেত্রে $\theta_1 = \theta_2 = 90^\circ$, ফলে $B = \frac{\mu_0 I}{4\pi d}(1 + 1) = \frac{\mu_0 I}{2\pi d}$। অর্ধ-অসীম তারের ক্ষেত্রে $\theta_1 = 0^\circ, \theta_2 = 90^\circ$, ফলে $B = \frac{\mu_0 I}{4\pi d}$।</t>
@@ -1269,11 +1264,6 @@
           <t>$n$ বাহুবিশিষ্ট একটি সুষম বহুভুজের প্রতিটি বাহুর দৈর্ঘ্য $a$ এবং এর মধ্য দিয়ে $I$ তড়িৎ প্রবাহিত হচ্ছে। বহুভুজটির কেন্দ্রে সৃষ্ট মোট চৌম্বক ক্ষেত্রের সাধারণ সমীকরণ প্রতিষ্ঠা করো এবং দেখাও যে $n \to \infty$ সীমায় এটি বৃত্তাকার কুণ্ডলীর কেন্দ্রে চৌম্বক ক্ষেত্রের সমীকরণে রূপান্তরিত হয়।</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>বহুভুজের কেন্দ্র থেকে যেকোনো একটি বাহুর লম্ব দূরত্ব $d = \frac{a/2}{\tan(\pi/n)} = \frac{a}{2 \tan(\pi/n)}$। বাহুর দুই প্রান্ত কেন্দ্রে $\frac{2\pi}{n}$ কোণ উৎপন্ন করে, ফলে লম্বের উভয়পাশে কোণ $\theta_1 = \theta_2 = \frac{\pi}{n}$। সসীম তারের সূত্র থেকে একটি বাহুর চৌম্বক ক্ষেত্র $B_1 = \frac{\mu_0 I}{4\pi d}(\sin \theta_1 + \sin \theta_2) = \frac{\mu_0 I}{4\pi \left(\frac{a}{2 \tan(\pi/n)}\right)} \cdot 2 \sin\left(\frac{\pi}{n}\right) = \frac{\mu_0 I}{\pi a} \sin\left(\frac{\pi}{n}\right) \tan\left(\frac{\pi}{n}\right)$। $n$ টি বাহুর কারণে কেন্দ্রের মোট ক্ষেত্র $B = n B_1 = \frac{\mu_0 n I}{\pi a} \sin\left(\frac{\pi}{n}\right) \tan\left(\frac{\pi}{n}\right)$। যখন $n \to \infty$, বহুভুজের পরিসীমা $n a \to 2 \pi R \implies a = \frac{2\pi R}{n}$। তখন $\sin(\pi/n) \approx \frac{\pi}{n}$ এবং $\tan(\pi/n) \approx \frac{\pi}{n}$। মান বসালে $B \to \frac{\mu_0 n I}{\pi (2\pi R/n)} \left(\frac{\pi}{n}\right)\left(\frac{\pi}{n}\right) = \frac{\mu_0 I}{2 R}$।</t>
@@ -1370,11 +1360,6 @@
           <t>হেলমহোল্টজ কুণ্ডলীতে (Helmholtz Coils) একই অক্ষ বিশিষ্ট সমান ব্যাসার্ধের ($R$) দুটি সমান্তরাল বৃত্তাকার কুণ্ডলীকে কেন ঠিক তাদের ব্যাসার্ধের সমান দূরত্বে ($d = R$) স্থাপন করা হয়? অক্ষীয় মধ্যবিন্দুতে ক্ষেত্রের দ্বিতীয় অন্তরক $\frac{d^2 B}{dx^2} = 0$ হওয়ার তাৎপর্য ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>দুটি কুণ্ডলীতে একই দিকে কারেন্ট চললে তাদের মধ্যবর্তী অক্ষের যেকোনো বিন্দুতে লব্ধি ক্ষেত্র $B(x) = B_1(x) + B_2(x)$। কুণ্ডলীদ্বয়ের কেন্দ্রবিন্দুদ্বয়ের মধ্যবিন্দুকে মূলবিন্দু ($x=0$) ধরলে কুণ্ডলী দুটির অবস্থান $-\frac{d}{2}$ এবং $+\frac{d}{2}$। টেলর ধারায় ক্ষেত্রের বিস্তার: $B(x) = B(0) + x B'(0) + \frac{x^2}{2!} B''(0) + \frac{x^3}{3!} B'''(0) + \frac{x^4}{4!} B^{(4)}(0) + \dots$। প্রতিসাম্যের কারণে সমস্ত বিজোড় অন্তরক শূন্য ($B'(0) = B'''(0) = 0$)। দ্বিতীয় অন্তরক $B''(0) = 0$ হওয়ার শর্ত সমাধান করলে সরাসরি পাওয়া যায় $d = R$। এর ফলে $x^4$ ক্রমের পূর্ব পর্যন্ত ক্ষেত্রের কোনো বিচ্যুতি থাকে না, যা পরীক্ষাগারে অতি নিখুঁত সুষম চৌম্বক ক্ষেত্র তৈরি করে।</t>
@@ -1420,11 +1405,6 @@
           <t>প্রতি একক দৈর্ঘ্যে $n$ পাক বিশিষ্ট এবং ব্যাসার্ধ $R$ বিশিষ্ট একটি সসীম সলিনয়েডের মধ্য দিয়ে $I$ তড়িৎ প্রবাহিত হচ্ছে। অক্ষের ওপর কোনো বিন্দুতে সলিনয়েডের দুই প্রান্তের কৌণিক উপবৃত্তদ্বয় যথাক্রমে $\alpha$ এবং $\beta$ কোণ তৈরি করলে অক্ষীয় চৌম্বক ক্ষেত্রের সমীকরণ প্রতিষ্ঠা করো।</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>সলিনয়েডের অক্ষ বরাবর $x$ অবস্থানে $dx$ পুরুত্বের একটি ফালিতে পাকসংখ্যা $dN = n dx$। অক্ষীয় একক লুপের ক্ষেত্রের সমীকরণ প্রয়োগ করে: $dB = \frac{\mu_0 (n dx I) R^2}{2 (R^2 + x^2)^{3/2}}$। কোণ রূপান্তর: $\cot \theta = \frac{x}{R} \implies x = R \cot \theta \implies dx = -R \csc^2 \theta d\theta$ এবং $R^2 + x^2 = R^2 \csc^2 \theta$। মান বসালে: $dB = -\frac{1}{2} \mu_0 n I \sin \theta d\theta$। সলিনয়েডের দুই প্রান্তের কোণ $\alpha$ থেকে $\beta$ পর্যন্ত সমাকলন করে: $B = -\frac{1}{2} \mu_0 n I \int_\alpha^\beta \sin \theta d\theta = \frac{1}{2} \mu_0 n I [\cos \theta]_\alpha^\beta = \frac{1}{2} \mu_0 n I (\cos \alpha - \cos \beta)$। একটি আদর্শ অসীম সলিনয়েডের অভ্যন্তরে $\alpha \to 0$ এবং $\beta \to \pi$, ফলে $B = \frac{1}{2}\mu_0 n I (1 - (-1)) = \mu_0 n I$। প্রান্তে $\alpha \to 0$ এবং $\beta = \pi/2$, ফলে $B = \frac{1}{2}\mu_0 n I$।</t>
@@ -1470,11 +1450,6 @@
           <t>ব্যাসার্ধ $R$ এবং সুষম পৃষ্ঠ আধান ঘনত্ব $\sigma$ বিশিষ্ট একটি পাতলা অন্তরক বৃত্তাকার চাকতি তার নিজস্ব অক্ষের সাপেক্ষে ধ্রুবক কৌণিক বেগ $\omega$-তে আবর্তিত হচ্ছে। চাকতিটির কেন্দ্রে সৃষ্ট চৌম্বক ক্ষেত্র $B$ নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>কেন্দ্র থেকে $r$ ব্যাসার্ধ ও $dr$ বেধের একটি বলয় বিবেচনা করি। এই বলয়ের ক্ষেত্রফল $dA = 2 \pi r dr$ এবং আধান $dq = \sigma 2 \pi r dr$। চাকতিটি $\omega$ কৌণিক বেগে ঘুরলে বলয়ের কার্যকর পর্যায়কাল $T = \frac{2\pi}{\omega}$। ফলে বলয়ের প্রবাহ $dI = \frac{dq}{T} = \frac{\sigma 2 \pi r dr}{2\pi / \omega} = \sigma \omega r dr$। কেন্দ্রে এই বলয়টির জন্য চৌম্বক ক্ষেত্র $dB = \frac{\mu_0 dI}{2 r} = \frac{\mu_0 (\sigma \omega r dr)}{2 r} = \frac{1}{2} \mu_0 \sigma \omega dr$। কেন্দ্র থেকে পরিধি পর্যন্ত সমগ্র চাকতির জন্য সমাকলন করে: $B = \int_0^R dB = \frac{1}{2} \mu_0 \sigma \omega \int_0^R dr = \frac{1}{2} \mu_0 \sigma \omega R$।</t>
@@ -1520,11 +1495,6 @@
           <t>গড় ব্যাসার্ধ $R$ এবং মোট $N$ পাক বিশিষ্ট একটি সুষম টরয়েডাল কয়েলে $I$ তড়িৎ প্রবাহিত হচ্ছে। বায়ো-সাভার্ট ও অ্যাম্পিয়ারের সূত্রের সাহায্যে প্রমাণ করো যে টরোয়েডের অভ্যন্তরীণ কোরে ক্ষেত্র $B = \frac{\mu_0 N I}{2 \pi R}$ হলেও টরোয়েডের উন্মুক্ত কেন্দ্রীয় গহ্বরে এবং বাইরের উন্মুক্ত স্থানে চৌম্বক ক্ষেত্র নিখুঁতভাবে শূন্য হয়।</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>টরোয়েডের কোর বরাবর $r$ ব্যাসার্ধের একটি অ্যাম্পিয়ার লুপ বিবেচনা করি। অ্যাম্পিয়ারের সূত্র: $\oint \vec{B} \cdot d\vec{\ell} = B (2\pi r) = \mu_0 I_{\text{enc}}$। কোরের ভেতর সমস্ত $N$ টি পাক আবদ্ধ থাকে, ফলে $I_{\text{enc}} = N I \implies B = \frac{\mu_0 N I}{2\pi r} = \mu_0 n I$। কেন্দ্রীয় উন্মুক্ত গহ্বরে যে কোনো লুপের ভেতর আবদ্ধ আধান বা প্রবাহ $I_{\text{enc}} = 0$, ফলে $B = 0$। টরোয়েডের বাইরের স্থানে কোনো লুপ নিলে কুণ্ডলীর প্রতিটি পাকের ভেতরের দিকে প্রবেশকারী প্রবাহ এবং বাইরের দিকে নির্গত হওয়া প্রবাহ পরস্পর বিপরীত হওয়ায় মোট আবদ্ধ প্রবাহ $I_{\text{enc}} = N I - N I = 0$, ফলে টরোয়েডের বাইরেও চৌম্বক ক্ষেত্র শূন্য হয়। এটি চৌম্বক ফ্লাক্সকে সম্পূর্ণ আবদ্ধ রাখার সেরা জ্যামিতি।</t>
@@ -1621,11 +1591,6 @@
           <t>একটি হাইড্রোজেন পরমাণুর বোর মডেলের প্রথম কক্ষপথে ($r = 0.53\text{ \AA}$) ইলেকট্রনটি $v \approx 2.18 \times 10^6\text{ m/s}$ দ্রুতিতে নিউক্লিয়াসকে প্রদক্ষিণ করছে। নিউক্লিয়াসের অবস্থানে ইলেকট্রনের কক্ষীয় গতির কারণে সৃষ্ট তুল্য চৌম্বক ক্ষেত্রের মান কত?</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>ইলেকট্রনের প্রদক্ষিণের পর্যায়কাল $T = \frac{2\pi r}{v}$। এর ফলে সমতুল্য বৃত্তাকার তড়িৎ প্রবাহ $I = \frac{e}{T} = \frac{e v}{2\pi r}$। একটি বৃত্তাকার প্রবাহের কেন্দ্রে চৌম্বক ক্ষেত্র $B = \frac{\mu_0 I}{2r}$। মান বসালে পাই: $B = \frac{\mu_0}{2r} \left(\frac{e v}{2\pi r}\right) = \frac{\mu_0 e v}{4 \pi r^2}$। মান বসিয়ে: $B = \frac{(10^{-7})(1.6 \times 10^{-19})(2.18 \times 10^6)}{(0.53 \times 10^{-10})^2} \approx \frac{3.488 \times 10^{-20}}{2.809 \times 10^{-21}} \approx 12.42\text{ T} \approx 12.5\text{ T}$। পরমাণুর অভ্যন্তরে নিউক্লিয়াসের ওপর ইলেকট্রন কর্তৃক সৃষ্ট এই তীব্র চৌম্বক ক্ষেত্রই পারমাণবিক বর্ণালির স্পিন-অরবিট কাপলিং ও ফাইন স্ট্রাকচার বিভাজনের কারণ।</t>
@@ -1671,11 +1636,6 @@
           <t>$R$ ব্যাসার্ধের একটি দীর্ঘ ধাতব তারের প্রস্থচ্ছেদ জুড়ে সুষমভাবে মোট $I$ তড়িৎ প্রবাহিত হচ্ছে। অ্যাম্পিয়ারের বর্তনী সূত্র প্রয়োগ করে অক্ষ থেকে $r$ দূরত্বে চৌম্বক ক্ষেত্রের সমীকরণ (ক) $r \le R$ এবং (খ) $r \ge R$ অঞ্চলের জন্য নির্ণয় করো। $B$ বনাম $r$ লেখচিত্রের বৈশিষ্ট্য কী?</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>ক) তারের অভ্যন্তরে ($r \le R$) $r$ ব্যাসার্ধের বৃত্তাকার অ্যাম্পিয়ারীয় লুপ নিলে আবদ্ধ প্রবাহ $I_{\text{enc}} = I \frac{\pi r^2}{\pi R^2} = I \frac{r^2}{R^2}$। অ্যাম্পিয়ারের সূত্রে: $\oint \vec{B} \cdot d\vec{\ell} = B (2\pi r) = \mu_0 I_{\text{enc}} = \mu_0 I \frac{r^2}{R^2} \implies B(r) = \frac{\mu_0 I r}{2\pi R^2}$। অর্থাৎ অক্ষ থেকে পরিধির দিকে ক্ষেত্র রৈখিকভাবে বৃদ্ধি পায় ($B \propto r$)। খ) তারের বাইরে ($r \ge R$) সম্পূর্ণ কারেন্ট আবদ্ধ থাকে, ফলে $I_{\text{enc}} = I$। অতএব $B (2\pi r) = \mu_0 I \implies B(r) = \frac{\mu_0 I}{2\pi r}$ ($B \propto 1/r$)। তারের পৃষ্ঠে ($r=R$) চৌম্বক ক্ষেত্র সর্বোচ্চ মান ধারণ করে: $B_{\max} = \frac{\mu_0 I}{2\pi R}$।</t>
@@ -1721,11 +1681,6 @@
           <t>$R$ ব্যাসার্ধের একটি দীর্ঘ বেলনাকার তারের ভেতর প্রবাহ ঘনত্ব অক্ষ থেকে দূরত্বের সাথে পরিবর্তিত হয়: $J(r) = k r$ (যেখানে $k$ একটি ধ্রুবক)। তারটির ভেতরে ($r &lt; R$) এবং বাইরে ($r &gt; R$) চৌম্বক ক্ষেত্রের সমীকরণ প্রতিষ্ঠা করো।</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>$r$ ব্যাসার্ধের অ্যাম্পিয়ার লুপের ভেতরে আবদ্ধ প্রবাহ সমাকলন করে পাওয়া যায়: $I_{\text{enc}} = \int_0^r J(r') 2\pi r' dr' = 2\pi k \int_0^r r'^2 dr' = \frac{2\pi k r^3}{3}$। অ্যাম্পিয়ারের সূত্রে: $B(r) 2\pi r = \mu_0 I_{\text{enc}} = \mu_0 \left(\frac{2\pi k r^3}{3}\right) \implies B(r) = \frac{\mu_0 k r^2}{3}$। তারের বাইরে ($r \ge R$) মোট আবদ্ধ প্রবাহ ধ্রুবক: $I_{\text{total}} = \frac{2\pi k R^3}{3}$। অতএব তারের বাইরে $B(r) 2\pi r = \mu_0 \left(\frac{2\pi k R^3}{3}\right) \implies B(r) = \frac{\mu_0 k R^3}{3 r}$।</t>
@@ -1771,11 +1726,6 @@
           <t>একটি সমাক্ষীয় তারের অভ্যন্তরীণ নিরেট পরিবাহীর ব্যাসার্ধ $a$ এবং বহিরাবরণী পাতলা নলের ব্যাসার্ধ $b$। উভয় পরিবাহীতে সমান মানের কিন্তু বিপরীতমুখী তড়িৎ $I$ প্রবাহিত হচ্ছে। (১) $r &lt; a$, (২) $a &lt; r &lt; b$, এবং (৩) $r &gt; b$ অঞ্চলে চৌম্বক ক্ষেত্রের মান কত? তারটির বাইরে কোনো চৌম্বক ক্ষেত্র থাকে না কেন?</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>১) অভ্যন্তরীণ পরিবাহীর ভেতরে ($r &lt; a$): $I_{\text{enc}} = I (r/a)^2 \implies B = \frac{\mu_0 I r}{2\pi a^2}$। ২) মধ্যবর্তী অঞ্চলে ($a &lt; r &lt; b$): কেবল ভেতরের পরিবাহীর কারেন্ট আবদ্ধ থাকে, ফলে $I_{\text{enc}} = I \implies B = \frac{\mu_0 I}{2\pi r}$। ৩) বহিঃস্থ অঞ্চলে ($r &gt; b$): যেকোনো অ্যাম্পিয়ার লুপের ভেতরে ভেতরের প্লাস কারেন্ট এবং বাইরের নলের মাইনাস কারেন্ট উভয়ই আবদ্ধ হয়। ফলে মোট নিট কারেন্ট $I_{\text{enc}} = +I - I = 0$। অ্যাম্পিয়ারের সূত্রানুযায়ী $B (2\pi r) = \mu_0 (0) \implies B = 0$। এই কারণেই উচ্চ কম্পাঙ্কের সংকেত পরিবহনে সমাক্ষীয় তার ব্যবহৃত হয় যাতে বাইরে কোনো চৌম্বকীয় বিকিরণ ও নয়েজ ছড়াতে না পারে।</t>
@@ -1821,11 +1771,6 @@
           <t>একটি অসীম বিস্তৃত সমতল পাতের তল বরাবর প্রতি একক প্রস্থে তলীয় প্রবাহ ঘনত্ব $\vec{K}$ প্রবাহিত হচ্ছে। অ্যাম্পিয়ারের বর্তনী সূত্র ব্যবহার করে পাতের উভয়পাশে উৎপন্ন চৌম্বক ক্ষেত্র $B = \frac{1}{2} \mu_0 K$ প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>সমতল পাতের সমমিতির কারণে চৌম্বক বলরেখাগুলো পাতের সমান্তরাল এবং প্রবাহ ও লম্বের সাথে পারস্পরিকভাবে লম্ব। পাতের উভয়পাশে $L$ দৈর্ঘ্য এবং $w$ প্রস্থের একটি আয়তাকার অ্যাম্পিয়ারীয় লুপ কল্পনা করি যার অর্ধেক পাতের উপরে এবং অর্ধেক নিচে বিস্তৃত। লুপের ওপর রেখা সমাকলন: $\oint \vec{B} \cdot d\vec{\ell} = B L + 0 + B L + 0 = 2 B L$ (প্রস্থের বাহুগুলো ক্ষেত্রের লম্ব হওয়ায় সমাকলন শূন্য)। লুপটির মধ্যে আবদ্ধ প্রবাহ $I_{\text{enc}} = K L$। অ্যাম্পিয়ারের সূত্রানুযায়ী: $2 B L = \mu_0 K L \implies B = \frac{1}{2} \mu_0 K$। লক্ষণীয় যে স্থিরতড়িৎ পাতের ক্ষেত্র $E = \frac{\sigma}{2\epsilon_0}$-এর ন্যায় এই চৌম্বক ক্ষেত্রটিও দূরত্ব নির্ভর নয়, বরং সম্পূর্ণরূপে সুষম।</t>
@@ -1871,11 +1816,6 @@
           <t>সুষম প্রবাহ ঘনত্ব $\vec{J}$ বিশিষ্ট একটি দীর্ঘ নিরেট বেলনাকার তারের অক্ষ থেকে $\vec{d}$ দূরত্বে একটি সমান্তরাল চোঙাকৃতি ফাঁকা গহ্বর (cylindrical cavity) খনন করা হলো। সুপারপজিশন নীতি ব্যবহার করে প্রমাণ করো যে গহ্বরের অভ্যন্তরে সর্বত্র চৌম্বক ক্ষেত্র সম্পূর্ণ সুষম এবং এর মান $\vec{B} = \frac{1}{2}\mu_0 (\vec{J} \times \vec{d})$।</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>সুপারপজিশন নীতি অনুসারে গহ্বরযুক্ত পরিবাহীকে দুটি অংশের উপরিপাতন ভাবা যায়: (১) সম্পূর্ণ নিরেট পরিবাহী যার প্রবাহ ঘনত্ব $+\vec{J}$, এবং (২) গহ্বরের স্থানে একই মাপের একটি কাল্পনিক পরিবাহী যার প্রবাহ ঘনত্ব $-\vec{J}$। নিরেট পরিবাহীর অক্ষ সাপেক্ষে কোনো বিন্দুর অবস্থান ভেক্টর $\vec{r}_1$ হলে তার ক্ষেত্র $\vec{B}_1 = \frac{1}{2}\mu_0 (\vec{J} \times \vec{r}_1)$। গহ্বরের অক্ষ সাপেক্ষে ঐ একই বিন্দুর অবস্থান ভেক্টর $\vec{r}_2$ হলে ঋণাত্মক প্রবাহের ক্ষেত্র $\vec{B}_2 = -\frac{1}{2}\mu_0 (\vec{J} \times \vec{r}_2)$। গহ্বরের ভেতরে লব্ধি ক্ষেত্র $\vec{B} = \vec{B}_1 + \vec{B}_2 = \frac{1}{2}\mu_0 \vec{J} \times (\vec{r}_1 - \vec{r}_2)$। কিন্তু ভেক্টর ত্রিভুজ থেকে মূল অক্ষ ও গহ্বরের অক্ষের দূরত্ব $\vec{d} = \vec{r}_1 - \vec{r}_2$। অতএব $\vec{B} = \frac{1}{2}\mu_0 (\vec{J} \times \vec{d})$। যেহেতু $\vec{d}$ একটি নির্দিষ্ট ধ্রুবক ভেক্টর, তাই গহ্বরের প্রতিটি বিন্দুতে চৌম্বক ক্ষেত্র অপরিবর্তনীয় ও সুষম থাকে।</t>
@@ -1921,11 +1861,6 @@
           <t>অ্যাম্পিয়ারের বর্তনী সূত্রের সমাকলন রূপ থেকে স্টোকসের উপপাদ্য প্রয়োগ করে এর ডিফারেনশিয়াল রূপ $\nabla \times \vec{B} = \mu_0 \vec{J}$ প্রতিষ্ঠা করো। স্থায়ী প্রবাহের জন্য এই সমীকরণ কীভাবে সন্ততি সমীকরণকে সিদ্ধ করে?</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>অ্যাম্পিয়ারের সমাকলন রূপ: $\oint \vec{B} \cdot d\vec{\ell} = \mu_0 I_{\text{enc}} = \mu_0 \iint \vec{J} \cdot d\vec{A}$। স্টোকসের কার্ল উপপাদ্য প্রয়োগ করে: $\oint \vec{B} \cdot d\vec{\ell} = \iint (\nabla \times \vec{B}) \cdot d\vec{A}$। উভয় ক্ষেত্র সমাকলন তুলনা করলে পাই: $\nabla \times \vec{B} = \mu_0 \vec{J}$। এটি অ্যাম্পিয়ারের ডিফারেনশিয়াল রূপ। যেকোনো ভেক্টর ক্ষেত্রের কার্লের ডাইভারজেন্স অভেদগতভাবে শূন্য: $\nabla \cdot (\nabla \times \vec{B}) \equiv 0$। ফলে $\mu_0 (\nabla \cdot \vec{J}) = 0 \implies \nabla \cdot \vec{J} = 0$। স্থির প্রবাহে আধানের ঘনত্ব অপরিবর্তিত থাকায় ($\frac{\partial \rho}{\partial t} = 0$) সন্ততি সমীকরণ $\nabla \cdot \vec{J} + \frac{\partial \rho}{\partial t} = 0$ নিখুঁতভাবে সন্তুষ্ট হয়।</t>
@@ -1971,11 +1906,6 @@
           <t>অভ্যন্তরীণ ব্যাসার্ধ $a$ এবং বহিঃস্থ ব্যাসার্ধ $b$ বিশিষ্ট একটি দীর্ঘ ফাঁপা ধাতব চোঙের দেয়ালের মধ্য দিয়ে সুষমভাবে $I$ প্রবাহ চলছে। (১) কেন্দ্রীয় শূন্য গহ্বরে ($r &lt; a$) এবং (২) ধাতুর দেয়ালের অভ্যন্তরে ($a \le r \le b$) চৌম্বক ক্ষেত্রের সমীকরণ লেখো।</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>১) কেন্দ্রীয় গহ্বরে ($r &lt; a$) কোনো পরিবাহী উপাদান নেই, ফলে আবদ্ধ প্রবাহ $I_{\text{enc}} = 0 \implies B = 0$। ২) দেয়ালের ভেতর ধাতুর প্রস্থচ্ছেদ ক্ষেত্রফল $A_{\text{wall}} = \pi(b^2 - a^2)$। প্রবাহ ঘনত্ব $J = \frac{I}{\pi(b^2 - a^2)}$। $r$ ব্যাসার্ধের লুপে আবদ্ধ ক্ষেত্রফল $\pi(r^2 - a^2)$, ফলে আবদ্ধ প্রবাহ $I_{\text{enc}} = J \pi(r^2 - a^2) = I \frac{r^2 - a^2}{b^2 - a^2}$। অ্যাম্পিয়ারের সূত্রে: $B (2\pi r) = \mu_0 I \frac{r^2 - a^2}{b^2 - a^2} \implies B(r) = \frac{\mu_0 I}{2\pi r}\left(\frac{r^2 - a^2}{b^2 - a^2}\right)$। যখন $r = a$, $B = 0$ এবং যখন $r = b$, $B = \frac{\mu_0 I}{2\pi b}$।</t>
@@ -2021,11 +1951,6 @@
           <t>দুটি ভিন্ন চৌম্বক মাধ্যমের বিভেদতলে কোনো মুক্ত তলীয় প্রবাহ না থাকলে ($\vec{K}_f = 0$) এবং মুক্ত তলীয় প্রবাহ থাকলে ($\vec{K}_f \neq 0$) চৌম্বক ক্ষেত্র $\vec{B}$-এর অভিলম্ব ও স্পর্শক উপাংশের বাউন্ডারি শর্তসমূহ প্রতিষ্ঠা করো।</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>গাউসের চৌম্বক সূত্র $\nabla \cdot \vec{B} = 0$-এর সমাকলন রূপ $\oint \vec{B} \cdot d\vec{A} = 0$ বিভেদতলে একটি ক্ষুদ্র পিলবক্সে প্রয়োগ করলে উভয়পাশের অভিলম্ব উপাংশ সমান হতে বাধ্য হয়: $B_{1n} = B_{2n}$। অর্থাৎ চৌম্বক ক্ষেত্রের অভিলম্ব উপাংশ সর্বদা অবিচ্ছিন্ন থাকে কারণ প্রকৃতিতে কোনো বিচ্ছিন্ন চৌম্বক একক মেরু নেই। অপরদিকে অ্যাম্পিয়ারের সূত্র $\oint \vec{B} \cdot d\vec{\ell} = \mu_0 I_{\text{enc}}$ বিভেদতল বরাবর একটি ক্ষুদ্র আয়তাকার লুপে প্রয়োগ করলে স্পর্শক উপাংশের বিয়োগফল পাওয়া যায়: $(B_{1t} - B_{2t}) L = \mu_0 K_f L \implies B_{1t} - B_{2t} = \mu_0 K_f$। যদি বিভেদতলে কোনো মুক্ত কারেন্ট না থাকে ($K_f = 0$), তবে স্পর্শক উপাংশও অবিচ্ছিন্ন থাকে ($B_{1t} = B_{2t}$)।</t>
@@ -2071,11 +1996,6 @@
           <t>চৌম্বক ক্ষেত্রে শক্তি সঞ্চিত থাকার রাশিমালা $u_B = \frac{B^2}{2 \mu_0}$ ব্যবহার করে $R$ ব্যাসার্ধের একটি দীর্ঘ সুষম পরিবাহী তারের নিজস্ব অভ্যন্তরে প্রতি একক দৈর্ঘ্যে সঞ্চিত চৌম্বক স্থিতিশক্তি ($U_{\text{in}} / L$) নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>তারের অভ্যন্তরে অক্ষ থেকে $r$ দূরত্বে চৌম্বক ক্ষেত্র $B(r) = \frac{\mu_0 I r}{2 \pi R^2}$। চৌম্বক শক্তি ঘনত্ব $u_B = \frac{B^2}{2 \mu_0} = \frac{1}{2 \mu_0} \left(\frac{\mu_0 I r}{2 \pi R^2}\right)^2 = \frac{\mu_0 I^2 r^2}{8 \pi^2 R^4}$। প্রতি একক দৈর্ঘ্যে $r$ থেকে $r+dr$ পুরুত্বের চোঙাকার খোলকের আয়তন $dV = 2 \pi r dr$। সমগ্র তারের অভ্যন্তরে একক দৈর্ঘ্যে সঞ্চিত মোট শক্তি: $\frac{U_{\text{in}}}{L} = \int_0^R u_B 2\pi r dr = \frac{\mu_0 I^2}{8 \pi^2 R^4} (2\pi) \int_0^R r^3 dr = \frac{\mu_0 I^2}{4 \pi R^4} \left[\frac{R^4}{4}\right] = \frac{\mu_0 I^2}{16 \pi}$। এই ফলাফলটি অসাধারণ কারণ এটি তারের ব্যাসার্ধ $R$-এর ওপর নির্ভর করে না; কেবল কারেন্টের ওপর নির্ভর করে।</t>
@@ -2121,11 +2041,6 @@
           <t>তারের অভ্যন্তরীণ চৌম্বক শক্তি $\frac{U_{\text{in}}}{L} = \frac{\mu_0 I^2}{16 \pi}$-কে আবেশকের শক্তির সমীকরণ $U = \frac{1}{2} L_{\text{in}} I^2$-এর সাথে তুলনা করে তারের অভ্যন্তরীণ স্বকীয় আবেশ গুণাঙ্ক (internal self-inductance per unit length) নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>আবেশকে সঞ্চিত শক্তির তাত্ত্বিক সমীকরণ $U = \frac{1}{2} L I^2$। প্রতি একক দৈর্ঘ্যের জন্য: $\frac{U_{\text{in}}}{L} = \frac{1}{2} \left(\frac{L_{\text{in}}}{L}\right) I^2$। পূর্ববর্তী প্রশ্নের ফলাফল থেকে আমরা জানি: $\frac{U_{\text{in}}}{L} = \frac{\mu_0 I^2}{16 \pi}$। সমীকরণ দুটি তুলনা করলে পাই: $\frac{1}{2} \left(\frac{L_{\text{in}}}{L}\right) I^2 = \frac{\mu_0 I^2}{16 \pi} \implies \frac{L_{\text{in}}}{L} = \frac{\mu_0}{8 \pi}$। শূন্যস্থানের ভেদনযোগ্যতা $\mu_0 = 4\pi \times 10^{-7}\text{ H/m}$ বসালে পাই: $\frac{L_{\text{in}}}{L} = \frac{4\pi \times 10^{-7}}{8\pi} = 0.5 \times 10^{-7}\text{ H/m} = 50\text{ nH/m}$।</t>
@@ -2171,11 +2086,6 @@
           <t>চৌম্বক ক্ষেত্রে গতিশীল আধানের ওপর প্রযুক্ত চৌম্বক লরেন্টজ বলের সমীকরণ $\vec{F}_B = q(\vec{v} \times \vec{B})$। ভেক্টর বিশ্লেষণ দ্বারা প্রমাণ করো যে চৌম্বক বল দ্বারা কোনো কণার ওপর কৃতকাজ সর্বদা নিখুঁতভাবে শূন্য হয়। এটি কণার গতিশক্তি ও বেগের অভিমুখকে কীভাবে প্রভাবিত করে?</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>চৌম্বক বল $\vec{F}_B = q(\vec{v} \times \vec{B})$ ভেক্টর গুণনের সংজ্ঞামতে বেগ $\vec{v}$ এবং চৌম্বক ক্ষেত্র $\vec{B}$ উভয়ের সাথে লম্ব। কণার ক্ষুদ্র সরণ $d\vec{r} = \vec{v} dt$। তাৎক্ষণিক ক্ষমতা $P = \vec{F}_B \cdot \vec{v} = q(\vec{v} \times \vec{B}) \cdot \vec{v}$। স্কেলার ট্রিপল প্রোডাক্টের নিয়মে দুটি ভেক্টর অভিন্ন হলে গুণফল শূন্য হয়: $(\vec{v} \times \vec{B}) \cdot \vec{v} \equiv 0$। ফলে ক্ষমতা $P = 0$ এবং কৃতকাজ $dW = P dt = 0$। কাজ-শক্তি উপপাদ্য অনুসারে $\Delta K = W = 0$। সুতরাং চৌম্বক ক্ষেত্র কণার গতিশক্তি এবং দ্রুতির কোনো পরিবর্তন ঘটাতে পারে না; এটি কেবল কেন্দ্রমুখী বল হিসেবে কাজ করে কণার গতিপথকে বক্র করে দেয়।</t>
@@ -2221,11 +2131,6 @@
           <t>একটি সুষম চৌম্বক ক্ষেত্র $\vec{B}$-এর সাথে $\theta$ কোণে $v$ বেগে একটি চার্জিত কণা ($q, m$) প্রবেশ করল। কণাটির গতিপথ হেলিক্স (সর্পিলাকার) হওয়ার কারণ ব্যাখ্যা করো। হেলিক্সের ব্যাসার্ধ $R$, পর্যায়কাল $T$ এবং পিচ (pitch, $p$)-এর রাশিমালা প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>বেগকে দুটি উপাংশে বিভক্ত করি: ক্ষেত্রের সমান্তরাল উপাংশ $v_{\parallel} = v \cos \theta$ এবং লম্ব উপাংশ $v_{\perp} = v \sin \theta$। লম্ব উপাংশের ওপর চৌম্বক বল $F = q v_{\perp} B$ কার্যকর হয় যা বৃত্তাকার গতি দেয়: $\frac{m v_{\perp}^2}{R} = q v_{\perp} B \implies R = \frac{m v_{\perp}}{q B} = \frac{m v \sin \theta}{q B}$। ঘূর্ণন পর্যায়কাল $T = \frac{2\pi R}{v_{\perp}} = \frac{2\pi m}{q B}$ (যা বেগ বা ব্যাসার্ধের ওপর স্বাধীন)। সমান্তরাল উপাংশের ওপর কোনো বল ক্রিয়া করে না ($F_{\parallel} = 0$), ফলে কণাটি সুষম বেগে অক্ষ বরাবর এগিয়ে যায়। এই দুই গতির মিলনে একটি হেলিক্স গঠিত হয়। একটি পূর্ণ ঘূর্ণনে অক্ষ বরাবর অতিক্রান্ত দূরত্বকে পিচ বলে: $p = v_{\parallel} T = (v \cos \theta)\left(\frac{2\pi m}{q B}\right) = \frac{2\pi m v \cos \theta}{q B}$।</t>
@@ -2269,11 +2174,6 @@
       <c r="G24" t="inlineStr">
         <is>
           <t>সাইক্লোট্রনের কার্যকরী মূলনীতি ব্যাখ্যা করো। সাইক্লোট্রন কম্পাঙ্ক $f_c = \frac{q B}{2\pi m}$ কেন কণার বেগ ও কক্ষপথের ব্যাসার্ধের ওপর নির্ভর করে না? ডি-দ্বয়ের প্রান্তীয় ব্যাসার্ধ $R$ হলে সাইক্লোট্রন থেকে নির্গত কণার সর্বোচ্চ গতিশক্তি $K_{\max}$-এর সমীকরণ প্রতিপাদন করো।</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2370,11 +2270,6 @@
           <t>পরস্পর লম্বভাবে স্থাপিত সুষম তড়িৎক্ষেত্র $\vec{E}$ এবং চৌম্বক ক্ষেত্র $\vec{B}$-এর মধ্য দিয়ে বিভিন্ন বেগের আধানের একটি মিশ্র রশ্মি প্রবেশ করানো হলো। কোনো বিচ্যুতি ছাড়া সোজা নির্গত হওয়ার জন্য কণার বেগ $v$-এর শর্ত প্রতিষ্ঠা করো। কণার আধান ও ভরের ওপর এই শর্ত নির্ভর করে কি?</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>তড়িৎক্ষেত্র $+y$ অভিমুখে এবং চৌম্বক ক্ষেত্র $+z$ অভিমুখে থাকলে $+x$ অভিমুখে গতিশীল ধনাত্মক আধানের ওপর তড়িৎ বল $\vec{F}_E = q E \hat{j}$ এবং চৌম্বক বল $\vec{F}_B = q(\vec{v} \times \vec{B}) = q (v \hat{i} \times B \hat{k}) = -q v B \hat{j}$। কোনো বিচ্যুতি না থাকার শর্ত হলো লব্ধি বল শূন্য হওয়া: $\vec{F}_{\text{net}} = \vec{F}_E + \vec{F}_B = 0 \implies q E - q v B = 0 \implies v = \frac{E}{B}$। সমীকরণটিতে আধান $q$ এবং ভর $m$ উভয়ই সম্পূর্ণরূপে কাটাকাটি হয়ে যায়। ফলে যে কোনো আধানযুক্ত বা যেকোনো ভরের কণা যদি ঠিক $v = E/B$ বেগে প্রবেশ করে, তবেই তা অবিচ্যুত অবস্থায় সরু ছিদ্র দিয়ে বেরিয়ে আসবে।</t>
@@ -2420,11 +2315,6 @@
           <t>জে জে থমসন কীভাবে ক্রসড তড়িৎ ও চৌম্বক ক্ষেত্র ব্যবহার করে ইলেকট্রনের নির্দিষ্ট আধান বা স্পেসিফিক চার্জ ($e/m$) পরিমাপ করেছিলেন? এর মূল গাণিতিক সমীকরণটি লেখো।</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>থমসন প্রথমে সমান্তরাল তড়িৎক্ষেত্র $E$ ও চৌম্বক ক্ষেত্র $B$ যুগপৎভাবে প্রয়োগ করে ফ্লুরোসেন্ট পর্দায় ক্যাথোড রশ্মির বিচ্যুতি শূন্য করেন, যা থেকে ইলেকট্রনের বেগ পাওয়া যায় $v = \frac{E}{B}$। এরপর চৌম্বক ক্ষেত্র বন্ধ করে কেবল তড়িৎক্ষেত্রে $L$ দৈর্ঘ্যের পাতে উল্লম্ব বিচ্যুতি $y$ পরিমাপ করেন: $y = \frac{1}{2} a t^2 = \frac{1}{2}\left(\frac{e E}{m}\right)\left(\frac{L}{v}\right)^2 = \frac{e E L^2}{2 m v^2}$। এখানে $v$-এর মান বসালে পাই: $y = \frac{e E L^2}{2 m (E/B)^2} = \frac{e B^2 L^2}{2 m E} \implies \frac{e}{m} = \frac{2 y E}{B^2 L^2}$। ১৮৯৭ সালে থমসন এই মান পান $\approx 1.76 \times 10^{11}\text{ C/kg}$, যা প্রমাণ করে যে ইলেকট্রন হাইড্রোজেনের চেয়ে প্রায় ১৮৩৭ গুণ হালকা একটি মৌলিক কণা।</t>
@@ -2470,11 +2360,6 @@
           <t>বেইনব্রীজ ভর বর্ণালীবীক্ষণ যন্ত্রে একটি বেগ নির্বাচক ($E, B_1$) এবং একটি পৃথক বিশ্লেষণ চৌম্বক ক্ষেত্র $B_2$ ব্যবহৃত হয়। একই আধান $q$-এর দুটি সমস্থানিক (isotopes)-এর ভর যথাক্রমে $m_1$ ও $m_2$ হলে ফটোগ্রাফিক প্লেটে তাদের আঘাত বিন্দুর মধ্যবর্তী দূরত্ব $\Delta x$-এর সমীকরণ প্রতিষ্ঠা করো।</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>বেগ নির্বাচক থেকে সমস্ত আয়ন সমান বেগে নির্গত হয়: $v = \frac{E}{B_1}$। এরপর আয়নগুলি লম্ব চৌম্বক ক্ষেত্র $B_2$-তে প্রবেশ করে অর্ধবৃত্তাকার পথ অতিক্রম করে ফটোগ্রাফিক প্লেটে আঘাত করে। বৃত্তাকার কক্ষপথের ব্যাসার্ধ $R = \frac{m v}{q B_2} = \frac{m E}{q B_1 B_2}$। প্লেটে প্রবেশের বিন্দু থেকে আঘাত বিন্দুর দূরত্ব হলো ব্যাস $x = 2 R$। দুটি ভিন্ন ভরের আইসোটোপের জন্য আঘাত বিন্দুর ব্যবধান $\Delta x = 2 R_2 - 2 R_1 = 2 \left(\frac{m_2 E}{q B_1 B_2} - \frac{m_1 E}{q B_1 B_2}\right) = \frac{2 E}{q B_1 B_2}(m_2 - m_1)$। এই দূরত্ব মেপে আইসোটোপের ভর ও প্রাচুর্য অতি নিখুঁতভাবে শনাক্ত করা যায়।</t>
@@ -2520,11 +2405,6 @@
           <t>অসম চৌম্বক ক্ষেত্রে যেখানে দুই প্রান্তে বলরেখাগুলো পরস্পরের সন্নিকটে এসে ক্ষেত্রের প্রাবল্য বৃদ্ধি পায়, সেখানে গতিশীল চার্জিত কণা কেন প্রতিফলিত হয়ে ফিরে আসে? চৌম্বক আয়না প্রভাব (Magnetic Mirror Effect) এবং প্লাজমা ট্র্যাপিংয়ের মূলনীতি ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>যখন কোনো কণা শক্তিশালী ক্ষেত্রের দিকে এগিয়ে যায়, তখন অপসারী বলরেখার কারণে কণার ওপর অক্ষের বিপরীতমুখী একটি লরেন্টজ বল উপাংশ ($F_z = -\mu \frac{\partial B_z}{\partial z}$) সৃষ্টি হয় যা কণাকে মন্দীভূত করে। কণার কক্ষীয় চৌম্বক মোমেন্ট $\mu = \frac{K_\perp}{B}$ প্রথম রুদ্ধতাপীয় ইনভেরিয়েন্ট হওয়ায় ধ্রুব থাকে। ফলে $B$ বৃদ্ধির সাথে সাথে লম্ব গতিশক্তি $K_\perp = \mu B$ বৃদ্ধি পেতে থাকে। মোট গতিশক্তি $K = K_\perp + K_\parallel$ ধ্রুব থাকায় সমান্তরাল গতিশক্তি $K_\parallel$ কমতে থাকে। যখন $K_\parallel = 0$ হয়, কণার অক্ষীয় বেগ শূন্য হয়ে যায় এবং এটি বিপরীত দিকে ফিরে আসে। দুই প্রান্তে শক্তিশালী চৌম্বক ক্ষেত্র তৈরি করে তৈরি 'চৌম্বক বোতল'-এ প্লাজমা বা পৃথিবীর ভ্যান অ্যালেন রেডিয়েশন বেল্টে কণা আটকে থাকে।</t>
@@ -2570,11 +2450,6 @@
           <t>নিউক্লিয়ার ফিউশন চুল্লিতে (যেমন ITER) ব্যবহৃত টোকামাক (Tokamak)-এ প্লাজমা আটকে রাখতে কেবল একটি সাধারণ টরয়েডাল চৌম্বক ক্ষেত্র যথেষ্ট নয় কেন? কেন একটি অতিরিক্ত পোলোইডাল ক্ষেত্র যুক্ত করে সর্পিলাকার (helical) ক্ষেত্র তৈরি করতে হয়?</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>একটি বিশুদ্ধ টরয়েডাল কয়েলে ভেতর দিকের ব্যাসার্ধ কম হওয়ায় চৌম্বক ক্ষেত্র বাইরে অপেক্ষা বেশি শক্তিশালী হয় ($\vec{\nabla} B \neq 0$)। এর ফলে অসম ক্ষেত্রে ধনাত্মক ও ঋণাত্মক আয়নগুলি বিপরীত দিকে স্থানচ্যুত হয় (গ্রেডিয়েন্ট ড্রিফট $v_{\nabla B} \propto \vec{B} \times \vec{\nabla} B$)। এই আধান বিভাজনের কারণে একটি উল্লম্ব স্থিরতড়িৎ ক্ষেত্র $\vec{E}$ তৈরি হয়। এই $\vec{E}$ এবং মূল $\vec{B}$ মিলে একটি বহির্মুখী ড্রিফট বেগ $\vec{v}_{E \times B} = \frac{\vec{E} \times \vec{B}}{B^2}$ তৈরি করে যা সমগ্র প্লাজমাকে সেকেন্ডের ভগ্নাংশে চুল্লির ধাতব দেয়ালে আছড়ে ফেলে ধ্বংস করে দেয়। টোকামাকে প্লাজমার মধ্য দিয়ে বিপুল কারেন্ট পাঠিয়ে একটি পোলোইডাল ক্ষেত্র সৃষ্টি করা হয়, ফলে চৌম্বক রেখাগুলো পেঁচানো হেলিক্সে পরিণত হয় এবং চার্জ বিচ্ছেদ স্বতঃস্ফূর্তভাবে প্রশমিত হয়।</t>
@@ -2620,11 +2495,6 @@
           <t>পরস্পর লম্ব সুষম ক্ষেত্র $\vec{E} = E \hat{j}$ এবং $\vec{B} = B \hat{k}$ বিদ্যমান অঞ্চলে মূলবিন্দু থেকে একটি স্থির আধান $+q$ ($v=0$) ছেড়ে দেওয়া হলো। কণাটির গতিপথ যে একটি সাইক্লয়েড (cycloid) হবে তা গতি সমীকরণ প্রতিষ্ঠা করে দেখাও এবং কণাটির ড্রিফট বেগের সমীকরণ লেখো।</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>লরেন্টজ বলের সমীকরণ: $m \frac{d\vec{v}}{dt} = q(\vec{E} + \vec{v} \times \vec{B})$। উপাংশে লিখলে: $m \dot{v}_x = q v_y B$ এবং $m \dot{v}_y = q E - q v_x B$। সাইক্লোট্রন কম্পাঙ্ক $\omega = \frac{q B}{m}$ সংজ্ঞায়িত করে ব্যবকলন সমীকরণ যুগল সমাধান করলে পাই: $v_x(t) = \frac{E}{B}(1 - \cos \omega t)$ এবং $v_y(t) = \frac{E}{B}\sin \omega t$। সময় সাপেক্ষে সমাকলন করলে স্থানাঙ্ক পাওয়া যায়: $x(t) = \frac{E}{\omega B}(\omega t - \sin \omega t)$ এবং $y(t) = \frac{E}{\omega B}(1 - \cos \omega t)$। এটি একটি রোলিং চাকার পরিধির বিন্দুর গতি নির্দেশ করে যা একটি আদর্শ সাইক্লয়েড বক্ররেখা। কণার নিট গড় গতি হয় $+x$ অভিমুখে ড্রিফট বেগ $v_{\text{drift}} = \frac{E}{B}$।</t>
@@ -2670,11 +2540,6 @@
           <t>তড়িৎবাহী তারের একটি ক্ষুদ্র অংশের ওপর চৌম্বক বলের রাশিমালা $d\vec{F} = I(d\vec{\ell} \times \vec{B})$ মুক্ত ইলেকট্রনের ওপর ক্রিয়াশীল লরেন্টজ বল থেকে প্রতিপাদন করো। প্রমাণ করো যে যেকোনো সুষম চৌম্বক ক্ষেত্রে স্থাপিত যেকোনো আকারের বদ্ধ পরিবাহী লুপের ওপর নিট চৌম্বক বল সর্বদা শূন্য হয় ($\oint d\vec{F} = 0$)।</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>$d\ell$ দৈর্ঘ্যের তারে মুক্ত ইলেকট্রন সংখ্যা $dN = n A d\ell$। প্রতিটি ইলেকট্রনের ওপর চৌম্বক বল $\vec{f} = -e (\vec{v}_d \times \vec{B})$। সমগ্র অংশের ওপর মোট বল $d\vec{F} = dN \cdot \vec{f} = n A d\ell [-e (\vec{v}_d \times \vec{B})] = -n e A (\vec{v}_d \times \vec{B}) d\ell$। প্রবাহ উপাদান $I d\vec{\ell} = -n e A \vec{v}_d d\ell$ বসালে পাই: $d\vec{F} = I (d\vec{\ell} \times \vec{B})$। একটি বদ্ধ লুপের জন্য মোট বল $\vec{F} = \oint I (d\vec{\ell} \times \vec{B})$। যদি $\vec{B}$ ক্ষেত্রটি সুষম হয়, তবে এটিকে সমাকলনের বাইরে নেওয়া যায়: $\vec{F} = I \left(\oint d\vec{\ell}\right) \times \vec{B}$। যেকোনো বদ্ধ বক্ররেখার সম্পূর্ণ ভেক্টর সরণ শূন্য ($\oint d\vec{\ell} = \vec{0}$)। অতএব $\vec{F} = I (\vec{0}) \times \vec{B} = \vec{0}$।</t>
@@ -2720,11 +2585,6 @@
           <t>শূন্যস্থানে পরস্পর থেকে $d$ দূরত্বে সমান্তরালে স্থাপিত দুটি দীর্ঘ সোজা তারের মধ্য দিয়ে যথাক্রমে $I_1$ ও $I_2$ প্রবাহ চললে প্রতি একক দৈর্ঘ্যে তাদের মধ্যকার পারস্পরিক ক্রিয়াশীল বলের রাশিমালা প্রতিপাদন করো। এর ভিত্তিতে এসআই এককে ১ অ্যাম্পিয়ার (১ A)-এর আন্তর্জাতিক সংজ্ঞা দাও।</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>প্রথম তারের কারেন্ট $I_1$-এর কারণে $d$ দূরত্বে দ্বিতীয় তারের অবস্থানে চৌম্বক ক্ষেত্র $B_1 = \frac{\mu_0 I_1}{2 \pi d}$। এই ক্ষেত্রের দিক ডান হাতের নিয়মে তারদ্বয়ের তলের সাথে লম্ব। দ্বিতীয় তারের $L$ দৈর্ঘ্যের ওপর এই ক্ষেত্রের কারণে প্রযুক্ত বল $F = I_2 L B_1 \sin 90^\circ = I_2 L \left(\frac{\mu_0 I_1}{2 \pi d}\right)$। অতএব প্রতি একক দৈর্ঘ্যে বল $\frac{F}{L} = \frac{\mu_0 I_1 I_2}{2 \pi d}$। যদি প্রবাহ একই দিকে হয় তবে আকর্ষণ বল এবং বিপরীত দিকে হলে বিকর্ষণ বল সৃষ্টি হয়। $I_1 = I_2 = 1\text{ A}$ এবং $d = 1\text{ m}$ বসালে $\frac{F}{L} = \frac{(4\pi \times 10^{-7})(1)(1)}{2\pi (1)} = 2 \times 10^{-7}\text{ N/m}$। এটিই ১ অ্যাম্পিয়ারের চিরায়ত ঐতিহাসিক সংজ্ঞা।</t>
@@ -2770,11 +2630,6 @@
           <t>$R$ ব্যাসার্ধের একটি নমনীয় বৃত্তাকার পরিবাহী তারে $I$ তড়িৎ প্রবাহিত হচ্ছে এবং কুণ্ডলীর তলের সাথে লম্বভাবে একটি সুষম চৌম্বক ক্ষেত্র $B$ বহির্মুখী প্রয়োগ করা হলো। তারটির উপাদানে সৃষ্ট যান্ত্রিক টান (Tension, $T$) নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>বৃত্তের পরিধির একটি অতিক্ষুদ্র বৃত্তচাপ $d\theta$ বিবেচনা করি যার দৈর্ঘ্য $d\ell = R d\theta$। এই অংশের মধ্য দিয়ে কারেন্ট $I$ চলায় এর ওপর বহির্মুখী ব্যাসার্ধীয় চৌম্বক বল $dF = I d\ell B = I (R d\theta) B$। এই ক্ষুদ্র অংশের দুই প্রান্তে স্পর্শকীয় টান $T$ ক্রিয়া করে। টানদ্বয়ের বহির্মুখী লম্ব উপাংশ $2 T \sin(d\theta / 2) \approx 2 T \left(\frac{d\theta}{2}\right) = T d\theta$। যান্ত্রিক ভারসাম্যে: $dF = T d\theta \implies I B R d\theta = T d\theta \implies T = I B R$। তারের প্রস্থচ্ছেদ ক্ষেত্রফল $A$ হলে উপাদানে সৃষ্ট টানপীড়ন $\sigma_{\text{stress}} = \frac{T}{A} = \frac{I B R}{A}$।</t>
@@ -2871,11 +2726,6 @@
           <t>$R$ ব্যাসার্ধের একটি অর্ধবৃত্তাকার তারের মধ্য দিয়ে $I$ তড়িৎ প্রবাহিত হচ্ছে। তারটির দুই প্রান্ত $A$ ও $B$ একটি সুষম চৌম্বক ক্ষেত্র $\vec{B}$-তে অবস্থিত যা তারের তলের সাথে লম্ব। তারটির ওপর মোট ক্রিয়াশীল বল কত?</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>সুষম চৌম্বক ক্ষেত্রে যেকোনো আকৃতির তারের ওপর মোট বল নির্ভর করে কেবল তার শুরুর বিন্দু ও শেষ বিন্দুর সরলরৈখিক ভেক্টর দূরত্বের ওপর: $\vec{F} = I (\vec{L}_{\text{net}} \times \vec{B})$। এখানে অর্ধবৃত্তাকার তারের শুরুর বিন্দু $A$ এবং শেষ বিন্দু $B$-এর মধ্যবর্তী সরলরৈখিক দূরত্ব হলো ব্যাস: $L_{\text{net}} = 2 R$। যেহেতু ক্ষেত্রটি তলের সাথে লম্ব, তাই বলের মান $F = I (2 R) B \sin 90^\circ = 2 I B R$। সমাকলন পদ্ধতির মাধ্যমেও একই ফলাফল পাওয়া যায়: $dF = I (R d\theta) B$, প্রতিসমতার কারণে সমান্তরাল উপাংশ যোগ হয়ে $\int_0^\pi I B R \sin \theta d\theta = I B R [-\cos \theta]_0^\pi = 2 I B R$।</t>
@@ -2921,11 +2771,6 @@
           <t>একই সমতলে স্থাপিত তিনটি দীর্ঘ সমান্তরাল তার $A, B, C$-এর মধ্য দিয়ে একই দিকে যথাক্রমে $I_1, I_2, I_3$ প্রবাহ চলছে। তার $A$ ও $C$-এর মধ্যবর্তী দূরত্ব $D$ হলে তার $B$-কে $A$ থেকে কত দূরত্বে স্থাপন করলে তার $B$-এর ওপর লব্ধি চৌম্বক বল শূন্য হবে?</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>ধরি তার $A$ থেকে তার $B$-এর দূরত্ব $x$, ফলে তার $C$ থেকে দূরত্ব $(D - x)$। তার $A$ কর্তৃক তার $B$-এর প্রতি একক দৈর্ঘ্যে আকর্ষণ বল $F_1 = \frac{\mu_0 I_1 I_2}{2\pi x}$ (বামমুখী)। তার $C$ কর্তৃক তার $B$-এর প্রতি একক দৈর্ঘ্যে আকর্ষণ বল $F_2 = \frac{\mu_0 I_3 I_2}{2\pi (D - x)}$ (ডানমুখী)। লব্ধি বল শূন্য হওয়ার শর্ত: $F_1 = F_2 \implies \frac{\mu_0 I_1 I_2}{2\pi x} = \frac{\mu_0 I_3 I_2}{2\pi (D - x)} \implies \frac{I_1}{x} = \frac{I_3}{D - x} \implies I_1(D - x) = I_3 x \implies I_1 D = (I_1 + I_3)x \implies x = \frac{I_1 D}{I_1 + I_3}$।</t>
@@ -2971,11 +2816,6 @@
           <t>প্রতি একক দৈর্ঘ্যে ভর $\lambda$ বিশিষ্ট একটি অনুভূমিক সোজা পরিবাহী তারের ঠিক নিচে $d$ দূরত্বে সমান্তরালে স্থাপিত অন্য একটি স্থির তারে $I_1$ প্রবাহ চলছে। উপরের তারটিকে বাতাসে কোনো অবলম্বন ছাড়াই স্থির ভাসমান (magnetic levitation) রাখতে তারটিতে কত প্রবাহ $I_2$ এবং কোন অভিমুখে পাঠাতে হবে?</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>উপরের তারটির একক দৈর্ঘ্যের ওজন খাড়া নিচের দিকে ক্রিয়া করে: $W/L = \lambda g$। এটিকে স্থির ভাসিয়ে রাখতে হলে ঊর্ধ্বমুখী বিকর্ষণ বল ওজনের সমান হতে হবে। বিকর্ষণ বল সৃষ্টির জন্য দুটি সমান্তরাল তারের প্রবাহ পরস্পর বিপরীতমুখী হতে হবে। তারদ্বয়ের প্রতি একক দৈর্ঘ্যে বিকর্ষণ বল $\frac{F}{L} = \frac{\mu_0 I_1 I_2}{2 \pi d}$। ভারসাম্যে: $\frac{\mu_0 I_1 I_2}{2 \pi d} = \lambda g \implies I_2 = \frac{2 \pi d \lambda g}{\mu_0 I_1}$।</t>
@@ -3021,11 +2861,6 @@
           <t>$R$ ব্যাসার্ধ ও $m$ ভর বিশিষ্ট একটি পাতলা রিংয়ে সুষমভাবে মোট $q$ আধান বণ্টিত আছে। রিংটি তার অক্ষের সাপেক্ষে $\omega$ কৌণিক বেগে ঘুরলে এর চৌম্বক দ্বিমেরু ভ্রামক $\mu$ এবং কৌণিক ভরবেগ $L$-এর অনুপাত ($\gamma = \mu / L$, জাইরোম্যাগনেটিক অনুপাত) কত হবে?</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>ঘূর্ণায়মান রিংয়ের কার্যকর প্রবাহ $I = \frac{q}{T} = \frac{q \omega}{2\pi}$। ক্ষেত্রফল $A = \pi R^2$। চৌম্বক দ্বিমেরু ভ্রামক $\mu = I A = \left(\frac{q \omega}{2\pi}\right)(\pi R^2) = \frac{1}{2} q \omega R^2$। রিংয়ের অক্ষীয় জড়তার ভ্রামক $I_{\text{inertia}} = m R^2$, ফলে কৌণিক ভরবেগ $L = I_{\text{inertia}} \omega = m R^2 \omega$। অনুপাত নিলে পাই: $\frac{\mu}{L} = \frac{\frac{1}{2} q \omega R^2}{m R^2 \omega} = \frac{q}{2m}$। এটি প্রমাণ করে যে যেকোনো আধানযুক্ত সমসত্ত্ব ঘূর্ণায়মান বস্তুর ক্ষেত্রে জাইরোম্যাগনেটিক অনুপাত সর্বদা একটি সার্বজনীন ধ্রুবক $\frac{q}{2m}$ হয়।</t>
@@ -3071,11 +2906,6 @@
           <t>$R$ ব্যাসার্ধ ও $M$ ভর বিশিষ্ট একটি নিরেট সুষম গোলকে সুষমভাবে $Q$ আধান বণ্টিত আছে। গোলকটি তার একটি ব্যাসের সাপেক্ষে $\omega$ কৌণিক বেগে আবর্তিত হলে এর চৌম্বক মোমেন্ট $\mu$ নির্ণয় করো এবং দেখাও যে এর জাইরোম্যাগনেটিক অনুপাত $\frac{\mu}{L} = \frac{Q}{2M}$ বজায় থাকে।</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>গোলকটিকে সমকেন্দ্রিক পাতলা খোলকে বা ডিস্কে বিভক্ত করে সমাকলন করা যায়। আধান ঘনত্ব $\rho = \frac{Q}{\frac{4}{3}\pi R^3}$ এবং ভর ঘনত্ব $\rho_m = \frac{M}{\frac{4}{3}\pi R^3}$। যেকোনো উপাদান $dV$-এর জন্য $dq = \rho dV$ এবং $dm = \rho_m dV$। প্রতি উপাদানের চৌম্বক মোমেন্ট $d\mu = \frac{1}{2} dq \omega r_\perp^2$ এবং কৌণিক ভরবেগ $dL = dm \omega r_\perp^2$। প্রতি উপাদানে $\frac{d\mu}{dL} = \frac{\rho}{2 \rho_m} = \frac{Q}{2M}$। যেহেতু অনুপাতটি স্থান-স্বাধীন ও ধ্রুবক, তাই সমগ্র গোলকের জন্য সমাকলন করলে সরাসরি পাই: $\frac{\mu}{L} = \frac{Q}{2M}$। নিরেট গোলকের জড়তার ভ্রামক $L = \frac{2}{5} M R^2 \omega$। অতএব চৌম্বক মোমেন্ট $\mu = \frac{Q}{2M} \left(\frac{2}{5} M R^2 \omega\right) = \frac{1}{5} Q \omega R^2$।</t>
@@ -3121,11 +2951,6 @@
           <t>$k$ স্প্রিং ধ্রুবকের দুটি অভিন্ন উল্লম্ব স্প্রিং দ্বারা $L$ দৈর্ঘ্যের এবং $m$ ভরের একটি অনুভূমিক ধাতব পরিবাহী দণ্ড ঝুলানো আছে। অনুভূমিকভাবে তলের সাথে লম্ব সুষম চৌম্বক ক্ষেত্র $B$ উপস্থিত। দণ্ডে $I$ কারেন্ট পাঠালে স্প্রিংদ্বয়ের প্রসারণ $\Delta x$-এর সমীকরণ প্রতিষ্ঠা করো।</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>দণ্ডটির নিজস্ব ওজন নিম্নমুখী: $W = m g$। পরিবাহীতে কারেন্ট চললে চৌম্বক বল $F_B = I L B$ উলম্বভাবে ক্রিয়া করে (কারেন্টের অভিমুখের ওপর নির্ভর করে খাড়া নিচের দিকে বা ওপরের দিকে)। দুটি স্প্রিং সমান্তরালে থাকায় তাদের মোট পুনরুদ্ধারকারী বল $2 k \Delta x$। যান্ত্রিক ভারসাম্যে: $2 k \Delta x = m g \pm I L B \implies \Delta x = \frac{m g \pm I L B}{2 k}$। এই নীতির সাহায্যে অত্যন্ত সংবেদনশীল বৈদ্যুতিক কারেন্ট পরিমাপক ব্যালান্স তৈরি করা হয়।</t>
@@ -3171,11 +2996,6 @@
           <t>একটি সমতল তড়িৎবাহী কুণ্ডলীর চৌম্বক দ্বিমেরু ভ্রামক $\vec{m} = I \vec{A}$। এটিকে একটি সুষম চৌম্বক ক্ষেত্র $\vec{B}$-তে স্থাপন করলে ক্রিয়াশীল টর্ক $\vec{\tau}$ এবং স্থিতিশক্তি $U$-এর পূর্ণাঙ্গ ভেক্টর সমীকরণ লেখো। সাম্যাবস্থা কখন স্থায়ী (stable) এবং কখন অস্থায়ী (unstable) হয়?</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>কুণ্ডলীর বিপরীত বাহুদ্বয়ের ওপর সমান ও বিপরীতমুখী বল যুগল টর্ক সৃষ্টি করে: $\tau = (I L_1 B) L_2 \sin \theta = I A B \sin \theta \implies \vec{\tau} = \vec{m} \times \vec{B}$। কৃতকাজ $dW = \tau d\theta = m B \sin \theta d\theta$। স্থিতিশক্তি $U = \int \tau d\theta = -m B \cos \theta = -\vec{m} \cdot \vec{B}$। যখন $\theta = 0^\circ$ (দ্বিমেরু ভ্রামক ক্ষেত্রের সমান্তরাল), তখন টর্ক শূন্য এবং স্থিতিশক্তি সর্বনিম্ন ($U = -m B$), যা স্থিতিশীল সাম্যাবস্থা নির্দেশ করে। যখন $\theta = 180^\circ$, তখন টর্ক শূন্য হলেও স্থিতিশক্তি সর্বোচ্চ ($U = +m B$), যা সামান্যতম বিচ্যুতিতে ঘুরে যায় অর্থাৎ অস্থিতিশীল সাম্যাবস্থা।</t>
@@ -3221,11 +3041,6 @@
           <t>বোর মডেলের সাহায্যে প্রমাণ করো যে পরমাণুতে ইলেকট্রনের কক্ষীয় চৌম্বক ভ্রামক এর কক্ষীয় কৌণিক ভরবেগের সমানুপাতিক ($\vec{\mu}_L = -\frac{e}{2 m_e} \vec{L}$)। বোর ম্যাগনেটন ($\mu_B$)-এর সংজ্ঞা দাও এবং মৌলিক ধ্রুবকগুলোর মাধ্যমে এর রাশিমালা ও সাংখ্যিক মান নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>কক্ষপথে আবর্তিত ইলেকট্রনের সমতুল্য প্রবাহ $I = \frac{e}{T} = \frac{e v}{2\pi r}$ এবং ক্ষেত্রফল $A = \pi r^2$। ফলে কক্ষীয় চৌম্বক ভ্রামক $\mu_L = I A = \frac{1}{2} e v r$। আবার কক্ষীয় কৌণিক ভরবেগ $L = m_e v r \implies v r = \frac{L}{m_e}$। মান বসালে: $\mu_L = \frac{e L}{2 m_e}$। ভেক্টর আকারে ইলেকট্রনের ঋণাত্মক আধানের দরুন $\vec{\mu}_L = -\frac{e}{2 m_e} \vec{L}$। বোরের প্রথম কোয়ান্টায়ন শর্তানুযায়ী প্রথম কক্ষপথে সর্বনিম্ন কৌণিক ভরবেগ $L = \hbar = \frac{h}{2\pi}$। এই অবস্থায় অর্জিত মৌলিক প্রাকৃতিক চৌম্বক ভ্রামকের একককেই বোর ম্যাগনেটন বলে: $\mu_B \equiv \frac{e \hbar}{2 m_e} = \frac{(1.602 \times 10^{-19})(1.055 \times 10^{-34})}{2 (9.109 \times 10^{-31})} \approx 9.274 \times 10^{-24}\text{ J/T}$।</t>
@@ -3271,11 +3086,6 @@
           <t>চলকুণ্ডলী গ্যালভানোমিটারে (Moving Coil Galvanometer) একটি সুষম ব্যাসার্ধীয় চৌম্বক ক্ষেত্র (Radial Magnetic Field) তৈরি করতে অবতল মেরুমুখ ও নরম লোহার সিলিন্ডার ব্যবহারের গুরুত্ব কী? কুণ্ডলীর কৌণিক বিক্ষেপ $\theta$ এবং প্রবাহ $I$-এর সম্পর্ক প্রতিষ্ঠা করো।</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>সাধারণ সমতল চৌম্বক ক্ষেত্রে কুণ্ডলী ঘুরলে টর্ক $\tau = N I A B \cos \theta$ কোণের সাথে পরিবর্তিত হয়, ফলে স্কেল রৈখিক হয় না। কিন্তু অবতল (concave) আকৃতির শক্তিশালী চৌম্বক মেরুর মাঝে নরম লোহার কোর রাখলে বলরেখাগুলো ব্যাসার্ধীয়ভাবে বিন্যস্ত হয়। এর ফলে কুণ্ডলী যে কোনো কোণে ঘুরুক না কেন, কুণ্ডলীর তল সর্বদা চৌম্বক বলরেখার সমান্তরাল থাকে, অর্থাৎ কুণ্ডলীর তলের অভিলম্ব সর্বদা ক্ষেত্রের সাথে ৯০ ডিগ্রি কোণ বজায় রাখে। ফলে বিক্ষেপক টর্ক সর্বদা ধ্রুবক থাকে: $\tau_{\text{def}} = N I A B$। কুণ্ডলীকে ধরে রাখা ফসফর-ব্রোঞ্জ তারের রিস্টোরিং টর্ক $\tau_{\text{res}} = C \theta$, যেখানে $C$ হলো টরশনাল ধ্রুবক। ভারসাম্যে: $N I A B = C \theta \implies \theta = \left(\frac{N A B}{C}\right) I$। অর্থাৎ বিক্ষেপ $\theta \propto I$, যা স্কেলকে সম্পূর্ণ রৈখিক করে।</t>
@@ -3321,11 +3131,6 @@
           <t>গ্যালভানোমিটারের প্রবাহ সংবেদনশীলতা (Current Sensitivity, $S_I$) এবং ভোল্টেজ সংবেদনশীলতা (Voltage Sensitivity, $S_V$)-এর সংজ্ঞা দাও। পাকসংখ্যা দ্বিগুণ করলে প্রবাহ সংবেদনশীলতা দ্বিগুণ হলেও ভোল্টেজ সংবেদনশীলতা কেন অপরিবর্তিত থাকে?</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>একক প্রবাহের জন্য সৃষ্ট বিক্ষেপকে কারেন্ট সংবেদনশীলতা বলে: $S_I = \frac{\theta}{I} = \frac{N A B}{C}$। একক ভোল্টেজের জন্য সৃষ্ট বিক্ষেপকে ভোল্টেজ সংবেদনশীলতা বলে: $S_V = \frac{\theta}{V} = \frac{\theta}{I R} = \frac{S_I}{R} = \frac{N A B}{C R}$। যদি পাকসংখ্যা $N$ বাড়িয়ে $2N$ করা হয়, তবে তারের মোট দৈর্ঘ্য দ্বিগুণ হয়, ফলে কুণ্ডলীর অভ্যন্তরীণ রোধও দ্বিগুণ হয়ে $2R$ হয়। নতুন ভোল্টেজ সংবেদনশীলতা $S_V' = \frac{(2N) A B}{C (2R)} = \frac{N A B}{C R} = S_V$। অতএব কুণ্ডলীর পাকসংখ্যা বাড়িয়ে কেবল কারেন্ট সংবেদনশীলতা বাড়ানো যায়, কিন্তু ভোল্টেজ সংবেদনশীলতা বাড়ানো যায় না।</t>
@@ -3371,11 +3176,6 @@
           <t>$G$ রোধের একটি গ্যালভানোমিটার সর্বোচ্চ $I_g$ প্রবাহ নিরাপদে পরিমাপ করতে পারে। এটিকে $0$ থেকে $I$ ($I &gt; I_g$) পরিসীমার একটি অ্যামিটারে রূপান্তর করতে সমান্তরালে কত মানের শান্ট রোধ $S$ যুক্ত করতে হবে? সমবায়ের তুল্য রোধের মান কত হবে?</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>গ্যালভানোমিটারের সমান্তরালে একটি অতিক্ষুদ্র রোধ $S$ (শান্ট) যুক্ত করা হয় যাতে অতিরিক্ত কারেন্ট শান্টের মধ্য দিয়ে বাইপাস হয়ে যায়। সমান্তরাল সমবায়ে উভয় শাখার বিভব সমান: $V_G = V_S \implies I_g G = (I - I_g) S \implies S = \frac{I_g G}{I - I_g}$। গুণন ক্ষমতা $n = \frac{I}{I_g}$ সংজ্ঞায়িত করলে $S = \frac{G}{n - 1}$। অ্যামিটারের মোট তুল্য রোধ $R_A = \frac{G S}{G + S}$। যেহেতু $S$ অত্যন্ত ক্ষুদ্র, তাই একটি আদর্শ অ্যামিটারের তুল্য রোধ শূন্যের কাছাকাছি হয় যাতে এটি কোনো বর্তনীতে শ্রেণীতে যুক্ত করলে মূল বর্তনীর প্রবাহে লক্ষণীয় পরিবর্তন না আনে।</t>
@@ -3421,11 +3221,6 @@
           <t>$G$ রোধ এবং $I_g$ পূর্ণ-স্কেল বিক্ষেপ কারেন্ট বিশিষ্ট একটি গ্যালভানোমিটারকে $0$ থেকে $V$ ভোল্ট পরিসীমার ভোল্টমিটারে রূপান্তর করতে কুণ্ডলীর সাথে শ্রেণীতে কত মানের একটি উচ্চ রোধ $R_s$ যুক্ত করতে হবে?</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>ভোল্টমিটারে রূপান্তরের জন্য গ্যালভানোমিটারের সাথে শ্রেণীতে একটি অতি উচ্চ মানের রোধ $R_s$ (মাল্টিপ্লায়ার) যুক্ত করা হয়। বর্তনীর মোট বিভব পতন $V = I_g (G + R_s) \implies G + R_s = \frac{V}{I_g} \implies R_s = \frac{V}{I_g} - G$। গ্যালভানোমিটারের নিজস্ব সর্বোচ্চ ভোল্টেজ সীমা $V_g = I_g G$ হলে গুণক $n = \frac{V}{V_g} = \frac{V}{I_g G}$। তখন সমীকরণটি দাঁড়ায় $R_s = G(n - 1)$। সম্পূর্ণ ভোল্টমিটারের মোট তুল্য রোধ $R_V = G + R_s \approx R_s$ অত্যন্ত উচ্চ (আদর্শ ক্ষেত্রে অসীম) হয় যাতে সমান্তরালে যুক্ত করলে এটি মূল বর্তনী থেকে নগণ্য কারেন্ট টানে।</t>
@@ -3471,11 +3266,6 @@
           <t>একটি সাধারণ চলকুণ্ডলী গ্যালভানোমিটার এবং একটি ব্যালাস্টিক গ্যালভানোমিটারের (Ballistic Galvanometer) মধ্যে মূল গঠনগত ও কার্যগত পার্থক্য কী? ক্ষণিক আধান $Q$-এর সাথে প্রথম বিক্ষেপ কোণ $\theta$-এর সমীকরণটি প্রতিষ্ঠা করো।</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>সাধারণ গ্যালভানোমিটারে কুণ্ডলী দ্রুত স্থির হয় (ডেড-বিট ড্যাম্পিং)। কিন্তু ব্যালাস্টিক গ্যালভানোমিটারের উদ্দেশ্য স্থির কারেন্ট মাপা নয়, বরং ক্ষণস্থায়ী আধানের স্পন্দন (যেমন ক্যাপাসিটরের ডিসচার্জ বা ইন্ডাকশনের ক্ষণিক প্রবাহ) পরিমাপ করা। এর কুণ্ডলীর জড়তার ভ্রামক $I$ অনেক বড় করা হয় এবং ড্যাম্পিং ন্যূনতম রাখা হয়, ফলে এর স্বাভাবিক পর্যায়কাল অনেক বড় হয় ($T \approx 10 - 15\text{ s}$)। কারেন্ট প্রবাহের সময়কাল $\Delta t \ll T$ হওয়ায় আধান প্রবাহ সম্পূর্ণ হওয়ার আগ পর্যন্ত কুণ্ডলীটি প্রায় নিশ্চল থাকে। অর্জিত কৌণিক ভরবেগ $\int \tau dt = N A B \int i dt = N A B Q$। এটি কুণ্ডলীর প্রাথমিক গতিশক্তি $\frac{1}{2} I \omega_0^2$-তে রূপান্তরিত হয় যা স্প্রিংয়ের স্থিতিশক্তি $\frac{1}{2} C \theta^2$-এর সমতুল্য হয়। সমাধান করে পাওয়া যায়: $Q = \left(\frac{C T}{2\pi N A B}\right) \theta$।</t>
@@ -3521,11 +3311,6 @@
           <t>$M$ চৌম্বক ভ্রামক বিশিষ্ট একটি অতিক্ষুদ্র দণ্ড চুম্বকের কেন্দ্র থেকে $r$ দূরত্বে (ক) অক্ষীয় অবস্থানে ($r \gg \ell$) এবং (খ) নিরক্ষীয় অবস্থানে চৌম্বক ক্ষেত্রের সমীকরণ প্রতিষ্ঠা করো। এদের অনুপাত কত?</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>তড়িৎ দ্বিমেরুর হুবহু সমতুল্যভাবে চৌম্বক দ্বিমেরু বিবেচনা করা যায় যেখানে মেরু শক্তি $m$ এবং চৌম্বক ভ্রামক $M = m (2\ell)$। ক) অক্ষীয় অবস্থানে দূরবর্তী বিন্দুতে ক্ষেত্র $B_{\text{axial}} = \frac{\mu_0}{4\pi}\left[\frac{m}{(r - \ell)^2} - \frac{m}{(r + \ell)^2}\right] = \frac{\mu_0}{4\pi} \frac{m (4 r \ell)}{(r^2 - \ell^2)^2} \approx \frac{\mu_0}{4\pi} \frac{2 M}{r^3}$। খ) নিরক্ষীয় তলে সমদ্বিবাহু ত্রিভুজ থেকে লব্ধি ক্ষেত্র $B_{\text{equatorial}} = 2 \left(\frac{\mu_0}{4\pi}\frac{m}{r^2 + \ell^2}\right) \cos \theta = \frac{\mu_0}{4\pi}\frac{m (2\ell)}{(r^2 + \ell^2)^{3/2}} \approx \frac{\mu_0}{4\pi} \frac{M}{r^3}$। সমান দূরত্বের জন্য অক্ষীয় ক্ষেত্র নিরক্ষীয় ক্ষেত্রের ঠিক দ্বিগুণ হয়।</t>
@@ -3571,11 +3356,6 @@
           <t>$I$ জড়তার ভ্রামক এবং $M$ চৌম্বক দ্বিমেরু ভ্রামক বিশিষ্ট একটি দণ্ড চুম্বককে অনুভূমিক সুষম চৌম্বক ক্ষেত্র $B$-তে মুক্তভাবে ঝুলিয়ে দিলে এর ক্ষুদ্র কৌণিক দোলনের পর্যায়কালের সমীকরণ প্রতিষ্ঠা করো।</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>সাম্যাবস্থা থেকে চুম্বকটিকে ক্ষুদ্র কোণ $\theta$-তে বিচ্যুত করলে পুনরুদ্ধারকারী টর্ক ক্রিয়া করে: $\tau = -M B \sin \theta \approx -M B \theta$। ঘূর্ণন গতির সমীকরণ $I \frac{d^2\theta}{dt^2} = -M B \theta \implies \frac{d^2\theta}{dt^2} + \left(\frac{M B}{I}\right)\theta = 0$। এটি কৌণিক সরল ছন্দিত স্পন্দন সমীকরণ যার কৌণিক কম্পাঙ্ক $\omega = \sqrt{\frac{M B}{I}}$। অতএব দোলনের পর্যায়কাল $T = \frac{2\pi}{\omega} = 2\pi \sqrt{\frac{I}{M B}}$। ভাইব্রেশন ম্যাগনেটোমিটারে এই সূত্র ব্যবহার করে দুটি চুম্বকের চৌম্বক ভ্রামক তুলনা বা কোনো স্থানের অনুভূমিক ভূ-চৌম্বক ক্ষেত্র $B_H$ নির্ণয় করা হয়।</t>
@@ -3621,11 +3401,6 @@
           <t>একটি ক্ষুদ্র চৌম্বক দ্বিমেরু $M$-এর কেন্দ্র থেকে $r$ দূরত্বে এবং দ্বিমেরু অক্ষের সাথে $\theta$ কোণে অবস্থিত যেকোনো বিন্দুতে লব্ধি চৌম্বক ক্ষেত্র $B$-এর মান এবং দিক নির্ণয়ের সমীকরণটি লেখো।</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>চৌম্বক ভ্রামক $\vec{M}$-কে দুটি লম্ব উপাংশে বিভক্ত করি: অবস্থান ভেক্টর $\vec{r}$ বরাবর উপাংশ $M_r = M \cos \theta$ এবং এর লম্ব উপাংশ $M_\theta = M \sin \theta$। অবস্থান ভেক্টর বরাবর ক্ষেত্র অক্ষীয় ক্ষেত্রের ন্যায়: $B_r = \frac{\mu_0}{4\pi}\frac{2 M \cos \theta}{r^3}$। লম্ব উপাংশ নিরক্ষীয় ক্ষেত্রের ন্যায়: $B_\theta = \frac{\mu_0}{4\pi}\frac{M \sin \theta}{r^3}$। লব্ধি ক্ষেত্রের মান: $B = \sqrt{B_r^2 + B_\theta^2} = \frac{\mu_0 M}{4\pi r^3}\sqrt{(2\cos \theta)^2 + (\sin \theta)^2} = \frac{\mu_0 M}{4\pi r^3}\sqrt{4\cos^2 \theta + (1 - \cos^2 \theta)} = \frac{\mu_0 M}{4\pi r^3}\sqrt{1 + 3\cos^2 \theta}$। অবস্থান ভেক্টরের সাথে লব্ধি ক্ষেত্রের কোণ $\alpha$ হলে $\tan \alpha = \frac{B_\theta}{B_r} = \frac{M \sin \theta}{2 M \cos \theta} = \frac{1}{2}\tan \theta$।</t>
@@ -3655,7 +3430,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>বৃত্তাকার কুণ্ডলীর কেন্দ্রে চৌম্বক ক্ষেত্র (সমস্যা 1)</t>
+          <t>বায়ো-সাভার্ট সূত্র, বৃত্তাকার কুণ্ডলী ও সলিনয়েড (Biot-Savart &amp; Solenoids)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3664,35 +3439,29 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>##PRESET:solenoid[size:medium]##
-[সমস্যা 1: বৃত্তাকার কুণ্ডলীর কেন্দ্রে চৌম্বক ক্ষেত্র]
-##PRESET:solenoid[size:medium]##
-$N = 400$ পাকসংখ্যা এবং $R = 4\text{ cm}$ ব্যাসার্ধবিশিষ্ট একটি সমতল বৃত্তাকার তারকুণ্ডলীতে $I = 2.5\text{ A}$ বিদ্যুৎ প্রবাহিত হচ্ছে। কুণ্ডলীর কেন্দ্রে চৌম্বক ক্ষেত্রের মান কত? ($\mu_0 = 4\pi \times 10^{-7}\text{ T}\cdot\text{m/A}$)</t>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি দীর্ঘ সোজা তারের মধ্য দিয়ে $I = 15.0\text{ A}$ তড়িৎ প্রবাহিত হচ্ছে। তারটি হতে লম্ব দূরত্ব $r = 5.0\text{ cm}$ দূরে চৌম্বক ক্ষেত্রের মান $B$ কত? ($\mu_0 = 4\pi \times 10^{-7}\text{ T}\cdot\text{m/A}$)।</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>##PRESET:solenoid[size:medium]##</t>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 1)।</t>
+          <t>অসীম সোজা তারের জন্য: $B = \frac{\mu_0 I}{2\pi r} = \frac{(4\pi \times 10^{-7}) \times 15.0}{2\pi \times 0.05} = \frac{2 \times 10^{-7} \times 15.0}{0.05} = \frac{3.0 \times 10^{-6}}{0.05} = 6.0 \times 10^{-5}\text{ T}$।</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>চৌম্বক ক্ষেত্র $B = 6.0 \times 10^{-5}\text{ T} = 0.60\text{ Gauss}$</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3712,12 +3481,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>দীর্ঘ ঋজু পরিবাহী ও বায়োট-স্যাভার্ট সূত্র (সমস্যা 2)</t>
+          <t>বায়ো-সাভার্ট সূত্র, বৃত্তাকার কুণ্ডলী ও সলিনয়েড (Biot-Savart &amp; Solenoids)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -3725,31 +3494,25 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>##PRESET:magnetic-field-wire[size:medium]##
-[সমস্যা 2: দীর্ঘ ঋজু পরিবাহী ও বায়োট-স্যাভার্ট সূত্র]
-##PRESET:magnetic-field-wire[size:medium]##
-একটি সোজা দীর্ঘ পরিবাহী তারের মধ্য দিয়ে $I = 60\text{ A}$ তড়িৎ প্রবাহিত হচ্ছে। তারটি হতে $d = 7\text{ cm}$ লম্ব দূরত্বে চৌম্বক ক্ষেত্রের মান কত টেসলা?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি বৃত্তাকার কুণ্ডলীর ব্যাসার্ধ $R = 10.0\text{ cm}$ এবং পাকসংখ্যা $N = 100$। কুণ্ডলীতে $I = 2.0\text{ A}$ প্রবাহ পাঠালে এর কেন্দ্রে চৌম্বক ক্ষেত্র $B_c$ কত এবং এর অক্ষের ওপর কেন্দ্র হতে $x = 10.0\text{ cm}$ দূরে চৌম্বক ক্ষেত্র $B_x$ কত?</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>##PRESET:magnetic-field-wire[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 2)।</t>
+          <t>কেন্দ্রে: $B_c = \frac{\mu_0 N I}{2R} = \frac{(4\pi \times 10^{-7}) \times 100 \times 2.0}{2 \times 0.10} = \frac{800\pi \times 10^{-7}}{0.20} = 4000\pi \times 10^{-7} \approx 1.2566 \times 10^{-3}\text{ T}$। অক্ষীয় বিন্দুতে: $B_x = \frac{\mu_0 N I R^2}{2(R^2 + x^2)^{3/2}} = B_c \frac{R^3}{(R^2 + x^2)^{3/2}}$। $x = R$ হলে $B_x = \frac{B_c}{2\sqrt{2}} = \frac{1.2566 \times 10^{-3}}{2.8284} \approx 4.443 \times 10^{-4}\text{ T}$।</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>কেন্দ্রে $B_c = 1.257 \times 10^{-3}\text{ T}$, অক্ষে $B_x = 4.44 \times 10^{-4}\text{ T}$</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3769,7 +3532,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>চৌম্বক ক্ষেত্রে গতিশীল আধানের ওপর লরেন্টজ বল (সমস্যা 3)</t>
+          <t>বায়ো-সাভার্ট সূত্র, বৃত্তাকার কুণ্ডলী ও সলিনয়েড (Biot-Savart &amp; Solenoids)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3778,29 +3541,29 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[সমস্যা 3: চৌম্বক ক্ষেত্রে গতিশীল আধানের ওপর লরেন্টজ বল]
-একটি প্রোটন ($q = 1.6 \times 10^{-19}\text{ C}$) $B = 0.8\text{ T}$ সুষম চৌম্বক ক্ষেত্রের সাথে লম্বভাবে $v = 10 \times 10^6\text{ m/s}$ বেগে প্রবেশ করল। প্রোটনটির ওপর ক্রিয়াশীল বল এবং এর বৃত্তাকার কক্ষপথের ব্যাসার্ধ কত? ($m = 1.67 \times 10^{-27}\text{ kg}$)</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+একটি দীর্ঘ সলিনয়েডের দৈর্ঘ্য $L = 50.0\text{ cm}$ এবং এতে মোট পাকসংখ্যা $N = 1000$। সলিনয়েডের মধ্য দিয়ে $I = 4.0\text{ A}$ কারেন্ট প্রবাহিত হলে এর অক্ষীয় কেন্দ্রে চৌম্বক ক্ষেত্র $B$ কত টেসলা?</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 3)।</t>
+          <t>একক দৈর্ঘ্যের পাকসংখ্যা $n = \frac{N}{L} = \frac{1000}{0.50} = 2000\text{ m}^{-1}$। সলিনয়েডের কেন্দ্রে: $B = \mu_0 n I = (4\pi \times 10^{-7}) \times 2000 \times 4.0 = 32\pi \times 10^{-4} \approx 1.0053 \times 10^{-2}\text{ T} = 10.05\text{ mT}$।</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 3</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>চৌম্বক ক্ষেত্র $B = 1.005 \times 10^{-2}\text{ T} \approx 10.05\text{ mT}$</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3820,12 +3583,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>সোলেনয়েডের অক্ষীয় চৌম্বক প্রাবল্য (সমস্যা 4)</t>
+          <t>বায়ো-সাভার্ট সূত্র, বৃত্তাকার কুণ্ডলী ও সলিনয়েড (Biot-Savart &amp; Solenoids)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -3833,25 +3596,25 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>[সমস্যা 4: সোলেনয়েডের অক্ষীয় চৌম্বক প্রাবল্য]
-$L = 0.10\text{ m}$ দীর্ঘ এবং $N = 1300$ পাকবিশিষ্ট একটি সোলেনয়েডের মধ্য দিয়ে $I = 4.0\text{ A}$ প্রবাহ চালনা করা হলে সোলেনয়েডের অভ্যন্তরে অক্ষীয় চৌম্বক আবেশ $B = \mu_0 n I$ কত টেসলা হবে?</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি টরয়েডের গড় ব্যাসার্ধ $r = 20.0\text{ cm}$ এবং মোট পাকসংখ্যা $N = 500$। টরয়েডটিতে $I = 3.0\text{ A}$ তড়িৎ পাঠালে এর অভ্যন্তরীণ অক্ষীয় বলয়ে চৌম্বক ক্ষেত্র কত হবে?</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 4)।</t>
+          <t>টরয়েডের পরিধি $2\pi r = 2\pi(0.20) = 0.40\pi\text{ m}$। চৌম্বক ক্ষেত্র $B = \frac{\mu_0 N I}{2\pi r} = \frac{(4\pi \times 10^{-7}) \times 500 \times 3.0}{0.40\pi} = \frac{6000\pi \times 10^{-7}}{0.40\pi} = 15000 \times 10^{-7} = 1.50 \times 10^{-3}\text{ T}$।</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 4</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>চৌম্বক ক্ষেত্র $B = 1.50 \times 10^{-3}\text{ T} = 1.50\text{ mT}$</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3871,7 +3634,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>সমান্তরাল পরিবাহী তারদ্বয়ের পারস্পরিক বল (সমস্যা 5)</t>
+          <t>বায়ো-সাভার্ট সূত্র, বৃত্তাকার কুণ্ডলী ও সলিনয়েড (Biot-Savart &amp; Solenoids)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3880,29 +3643,29 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[সমস্যা 5: সমান্তরাল পরিবাহী তারদ্বয়ের পারস্পরিক বল]
-পরস্পর হতে $d = 12\text{ cm}$ দূরত্বে অবস্থিত দুটি সমান্তরাল পরিবাহী তারের মধ্য দিয়ে যথাক্রমে $I_1 = 1\text{ A}$ এবং $I_2 = 15\text{ A}$ বিদ্যুৎ একই দিকে প্রবাহিত হচ্ছে। তার দুটির প্রতি মিটার দৈর্ঘ্যে আকর্ষণ বলের মান কত?</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+দুটি দীর্ঘ সমান্তরাল পরিবাহী তারের মধ্যবর্তী দূরত্ব $d = 20\text{ cm}$। তার দুটিতে যথাক্রমে $I_1 = 10\text{ A}$ এবং $I_2 = 20\text{ A}$ তড়িৎ একই অভিমুখে প্রবাহিত হচ্ছে। তারদ্বয়ের সংযোগকারী রেখার মধ্যবিন্দুতে লব্ধি চৌম্বক ক্ষেত্র $B$ কত?</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 5)।</t>
+          <t>মধ্যবিন্দুতে উভয় তার হতে দূরত্ব $r_1 = r_2 = 10\text{ cm} = 0.10\text{ m}$। একই দিকে প্রবাহ হওয়ায় ডানহাত নিয়ম অনুসারে মধ্যবিন্দুতে তার দুটির চৌম্বক ক্ষেত্র পরস্পর বিপরীতমুখী হবে: $B_1 = \frac{\mu_0 I_1}{2\pi r} = \frac{(2 \times 10^{-7})(10)}{0.10} = 2.0 \times 10^{-5}\text{ T}$। $B_2 = \frac{\mu_0 I_2}{2\pi r} = \frac{(2 \times 10^{-7})(20)}{0.10} = 4.0 \times 10^{-5}\text{ T}$। লব্ধি $B = B_2 - B_1 = 4.0 \times 10^{-5} - 2.0 \times 10^{-5} = 2.0 \times 10^{-5}\text{ T}$ ($I_2$-এর প্রভাব অভিমুখে)।</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 5</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>লব্ধি চৌম্বক ক্ষেত্র $B = 2.0 \times 10^{-5}\text{ T}$</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3922,12 +3685,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>তড়িৎবাহী কুণ্ডলীর ওপর প্রযুক্ত টর্ক (সমস্যা 6)</t>
+          <t>বায়ো-সাভার্ট সূত্র, বৃত্তাকার কুণ্ডলী ও সলিনয়েড (Biot-Savart &amp; Solenoids)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -3935,25 +3698,25 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[সমস্যা 6: তড়িৎবাহী কুণ্ডলীর ওপর প্রযুক্ত টর্ক]
-একটি $N = 20$ পাকের আয়তাকার কুণ্ডলীর দৈর্ঘ্য $10\text{ cm}$ ও প্রস্থ $5\text{ cm}$। কুণ্ডলীটির মধ্য দিয়ে $I = 2\text{ A}$ প্রবাহ চলছে এবং এটি $B = 0.4\text{ T}$ চৌম্বক ক্ষেত্রের সাথে সমান্তরালে স্থাপিত। কুণ্ডলীটির ওপর প্রযুক্ত টর্ক $\tau = NIAB$ কত?</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি বৃত্তাকার কুণ্ডলীর কেন্দ্রে চৌম্বক ক্ষেত্র $B_0$। কেন্দ্র হতে এর অক্ষ বরাবর কত দূরত্বে চৌম্বক ক্ষেত্রের মান কেন্দ্রের মানের $rac{1}{8}$ অংশ হবে? (কুণ্ডলীর ব্যাসার্ধ $R$)।</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 6)।</t>
+          <t>অক্ষীয় প্রাবল্য $B_x = B_0 \frac{R^3}{(R^2 + x^2)^{3/2}} = \frac{B_0}{8} \implies \frac{R^3}{(R^2 + x^2)^{3/2}} = \frac{1}{8}$। উভয়পক্ষে ঘনমূল নিয়ে: $\frac{R}{\sqrt{R^2 + x^2}} = \frac{1}{2} \implies \sqrt{R^2 + x^2} = 2R$। বর্গ করে: $R^2 + x^2 = 4R^2 \implies x^2 = 3R^2 \implies x = \sqrt{3} R$।</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 6</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>দূরত্ব $x = \sqrt{3} R \approx 1.732 R$</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3973,7 +3736,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>সাইক্লোট্রন কম্পাঙ্ক ও পর্যায়কাল (সমস্যা 7)</t>
+          <t>বায়ো-সাভার্ট সূত্র, বৃত্তাকার কুণ্ডলী ও সলিনয়েড (Biot-Savart &amp; Solenoids)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3982,29 +3745,29 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[সমস্যা 7: সাইক্লোট্রন কম্পাঙ্ক ও পর্যায়কাল]
-$B = 4.0\text{ T}$ চৌম্বক ক্ষেত্রে একটি ইলেকট্রন বৃত্তাকার কক্ষপথে আবর্তন করছে। ইলেকট্রনটির সাইক্লোট্রন কম্পাঙ্ক ($f = \frac{qB}{2\pi m}$) কত মেগাহার্টজ (MHz) হবে?</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+হেলমহোল্টজ কয়েল যুগল: সমান ব্যাসার্ধের ($R = 15\text{ cm}$) এবং সমান পাকসংখ্যার ($N = 100$) দুটি বৃত্তাকার কুণ্ডলী পরস্পর $d = R = 15\text{ cm}$ দূরত্বে সমাক্ষীয়ভাবে অবস্থিত। উভয়টিতে একই দিকে $I = 1.0\text{ A}$ প্রবাহ পাঠালে কুণ্ডলীদ্বয়ের ঠিক মধ্যবিন্দুতে অতি সুষম চৌম্বক ক্ষেত্র $B$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 7)।</t>
+          <t>হেলমহোল্টজ কয়েলের মধ্যবিন্দুতে উভয় কয়েল হতে দূরত্ব $x = R/2$। প্রতিটি কয়েলের অবদান $B_1 = \frac{\mu_0 N I R^2}{2(R^2 + R^2/4)^{3/2}} = \frac{\mu_0 N I}{2 R (5/4)^{3/2}} = \frac{4}{5\sqrt{5}}\frac{\mu_0 N I}{2R}$। উভয় কয়েল যোগ হয়ে মোট ক্ষেত্র $B = 2 B_1 = \left(\frac{8}{5\sqrt{5}}\right)\frac{\mu_0 N I}{R} = \frac{8}{5\sqrt{5}}\frac{(4\pi \times 10^{-7}) \times 100 \times 1.0}{0.15} \approx 0.7155 \times 8.3776 \times 10^{-4} \approx 5.994 \times 10^{-4}\text{ T}$।</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 7</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>সুষম চৌম্বক ক্ষেত্র $B = 5.99 \times 10^{-4}\text{ T}$</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4024,12 +3787,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ভূ-চৌম্বকত্বের আনুভূমিক উপাংশ ও বিনতি কোণ (সমস্যা 8)</t>
+          <t>বায়ো-সাভার্ট সূত্র, বৃত্তাকার কুণ্ডলী ও সলিনয়েড (Biot-Savart &amp; Solenoids)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -4037,25 +3800,25 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>[সমস্যা 8: ভূ-চৌম্বকত্বের আনুভূমিক উপাংশ ও বিনতি কোণ]
-কোনো স্থানে পৃথিবীর মোট চৌম্বক ক্ষেত্রের মান $B = 4 \times 10^{-5}\text{ T}$ এবং বিনতি কোণ $\delta = 60^\circ$। ঐ স্থানে ভূ-চৌম্বক ক্ষেত্রের আনুভূমিক উপাংশ ($B_H = B\cos\delta$) এবং উলম্ব উপাংশ ($B_V$) কত?</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>##GEO:triangle[b=3,h=3][size:small]##
+একটি সুষম তার দিয়ে গঠিত $a = 10\text{ cm}$ বাহুবিশিষ্ট সমবাহু ত্রিভুজাকার কুণ্ডলীর মধ্য দিয়ে $I = 3.0\text{ A}$ তড়িৎ প্রবাহিত হলে এর ভরকেন্দ্রে (Centroid) উৎপন্ন চৌম্বক ক্ষেত্র কত?</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>##GEO:triangle[b=3,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 8)।</t>
+          <t>ভরকেন্দ্র হতে প্রতিটি বাহুর লম্ব দূরত্ব $r = \frac{a}{2\sqrt{3}} = \frac{0.10}{2\sqrt{3}} = \frac{0.05}{\sqrt{3}}\text{ m}$। প্রতিটি বাহুর দুই প্রান্তের কোণ $\theta_1 = \theta_2 = 60^\circ$। একটি বাহুর অবদান $B_1 = \frac{\mu_0 I}{4\pi r}(\sin 60^\circ + \sin 60^\circ) = \frac{(10^{-7})(3.0)}{\frac{0.05}{\sqrt{3}}}(2 \times \frac{\sqrt{3}}{2}) = \frac{3 \times 10^{-7} \times 3}{0.05} = 1.80 \times 10^{-5}\text{ T}$। ৩টি বাহুর অবদান একই দিকে যোগ হওয়ায় মোট ক্ষেত্র $B = 3 B_1 = 3 \times 1.80 \times 10^{-5} = 5.40 \times 10^{-5}\text{ T}$।</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 8</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>ভরকেন্দ্রে চৌম্বক ক্ষেত্র $B = 5.40 \times 10^{-5}\text{ T}$</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4075,7 +3838,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>অ্যাম্পিয়ারের চক্রীয় সূত্র ও টরয়েড (সমস্যা 9)</t>
+          <t>বায়ো-সাভার্ট সূত্র, বৃত্তাকার কুণ্ডলী ও সলিনয়েড (Biot-Savart &amp; Solenoids)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4084,29 +3847,29 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[সমস্যা 9: অ্যাম্পিয়ারের চক্রীয় সূত্র ও টরয়েড]
-একটি টরয়েডের গড় ব্যাসার্ধ $R = 80\text{ cm}$ এবং মোট পাকসংখ্যা $N = 13000$। এর মধ্য দিয়ে $I = 3\text{ A}$ তড়িৎ প্রবাহিত হলে টরয়েডের অভ্যন্তরে চৌম্বক ক্ষেত্রের মান কত?</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি বৃত্তাকার আর্কের কোণ $	heta = rac{\pi}{3} = 60^\circ$ এবং ব্যাসার্ধ $R = 5.0\text{ cm}$। আর্কে $I = 6.0\text{ A}$ কারেন্ট চললে কেন্দ্রে চৌম্বক ক্ষেত্র কত?</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 9)।</t>
+          <t>সম্পূর্ণ বৃত্তের জন্য $B_{\text{full}} = \frac{\mu_0 I}{2R}$। কোণ $\theta$ হলে $B = \frac{\mu_0 I}{4\pi R}\theta = \frac{(4\pi \times 10^{-7}) \times 6.0}{4\pi \times 0.05} \times \frac{\pi}{3} = \frac{6 \times 10^{-7}}{0.05} \times 1.0472 = (1.2 \times 10^{-5}) \times 1.0472 \approx 1.2566 \times 10^{-5}\text{ T}$।</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 9</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>কেন্দ্রে চৌম্বক ক্ষেত্র $B = 1.257 \times 10^{-5}\text{ T}$</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4126,12 +3889,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>চৌম্বক ভ্রামক ও পরমাণুর বোর ম্যাগনেটন (সমস্যা 10)</t>
+          <t>বায়ো-সাভার্ট সূত্র, বৃত্তাকার কুণ্ডলী ও সলিনয়েড (Biot-Savart &amp; Solenoids)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -4139,25 +3902,25 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[সমস্যা 10: চৌম্বক ভ্রামক ও পরমাণুর বোর ম্যাগনেটন]
-একটি বৃত্তাকার হাইড্রোজেন কক্ষপথে ইলেকট্রন প্রতি সেকেন্ডে $f = 10 \times 10^{15}$ বার ঘোরে। কক্ষপথের ব্যাসার্ধ $r = 0.53\text{ \AA}$ হলে এর সমতুল্য চৌম্বক দ্বিমেরু ভ্রামক ($M = I A$) কত?</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি সরু সোজা তারে $I = 10\text{ A}$ প্রবাহ চলছে। তারটির $L = 20\text{ cm}$ দৈর্ঘ্যের একটি অংশের জন্য তারের লম্ব সমদ্বিখণ্ডকের ওপর $d = 10\text{ cm}$ দূরত্বে চৌম্বক ক্ষেত্র কত?</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 10)।</t>
+          <t>প্রান্তদ্বয়ের কোণ $\tan\theta = \frac{L/2}{d} = \frac{10}{10} = 1 \implies \theta = 45^\circ$। $B = \frac{\mu_0 I}{4\pi d}(\sin 45^\circ + \sin 45^\circ) = \frac{(10^{-7})(10)}{0.10}(2 \times \frac{1}{\sqrt{2}}) = 10^{-5} \times \sqrt{2} \approx 1.414 \times 10^{-5}\text{ T}$।</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 10</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>চৌম্বক ক্ষেত্র $B = 1.414 \times 10^{-5}\text{ T}$</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4177,44 +3940,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>বৃত্তাকার কুণ্ডলীর কেন্দ্রে চৌম্বক ক্ষেত্র (সমস্যা 11)</t>
+          <t>লরেঞ্জ বল, সাইক্লোট্রন ও তারের ওপর চৌম্বক বল (Lorentz Force &amp; Cyclotron)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>##PRESET:solenoid[size:medium]##
-[সমস্যা 11: বৃত্তাকার কুণ্ডলীর কেন্দ্রে চৌম্বক ক্ষেত্র]
-##PRESET:solenoid[size:medium]##
-$N = 1200$ পাকসংখ্যা এবং $R = 4\text{ cm}$ ব্যাসার্ধবিশিষ্ট একটি সমতল বৃত্তাকার তারকুণ্ডলীতে $I = 2.5\text{ A}$ বিদ্যুৎ প্রবাহিত হচ্ছে। কুণ্ডলীর কেন্দ্রে চৌম্বক ক্ষেত্রের মান কত? ($\mu_0 = 4\pi \times 10^{-7}\text{ T}\cdot\text{m/A}$)</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি প্রোটন ($q = 1.6 \times 10^{-19}\text{ C}, m = 1.67 \times 10^{-27}\text{ kg}$) একটি সুষম চৌম্বক ক্ষেত্র $B = 0.50\text{ T}$-এ লম্বভাবে $v = 2.0 \times 10^6\text{ m/s}$ বেগে প্রবেশ করল। প্রোটনটির বৃত্তাকার কক্ষপথের ব্যাসার্ধ $r$, পর্যায়কাল $T$ এবং সাইক্লোট্রন কম্পাঙ্ক $f_c$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>##PRESET:solenoid[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 11)।</t>
+          <t>চৌম্বক বল কেন্দ্রমুখী বল যোগায়: $q v B = \frac{m v^2}{r} \implies r = \frac{m v}{q B} = \frac{(1.67 \times 10^{-27}) \times (2.0 \times 10^6)}{(1.6 \times 10^{-19}) \times 0.50} = \frac{3.34 \times 10^{-21}}{8.0 \times 10^{-20}} = 0.04175\text{ m} = 4.175\text{ cm}$। পর্যায়কাল $T = \frac{2\pi m}{q B} = \frac{2\pi (1.67 \times 10^{-27})}{8.0 \times 10^{-20}} \approx 1.3116 \times 10^{-7}\text{ s}$। সাইক্লোট্রন কম্পাঙ্ক $f_c = \frac{1}{T} \approx 7.624 \times 10^6\text{ Hz} = 7.62\text{ MHz}$।</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 11</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>কক্ষপথের ব্যাসার্ধ $r = 4.175\text{ cm}$, পর্যায়কাল $T = 1.312 \times 10^{-7}\text{ s}$, সাইক্লোট্রন কম্পাঙ্ক $f_c = 7.62\text{ MHz}$</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4234,7 +3991,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>দীর্ঘ ঋজু পরিবাহী ও বায়োট-স্যাভার্ট সূত্র (সমস্যা 12)</t>
+          <t>লরেঞ্জ বল, সাইক্লোট্রন ও তারের ওপর চৌম্বক বল (Lorentz Force &amp; Cyclotron)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4247,31 +4004,25 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>##PRESET:magnetic-field-wire[size:medium]##
-[সমস্যা 12: দীর্ঘ ঋজু পরিবাহী ও বায়োট-স্যাভার্ট সূত্র]
-##PRESET:magnetic-field-wire[size:medium]##
-একটি সোজা দীর্ঘ পরিবাহী তারের মধ্য দিয়ে $I = 20\text{ A}$ তড়িৎ প্রবাহিত হচ্ছে। তারটি হতে $d = 7\text{ cm}$ লম্ব দূরত্বে চৌম্বক ক্ষেত্রের মান কত টেসলা?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি আলফা কণা ($q = +2e, m = 6.64 \times 10^{-27}\text{ kg}$) এবং একটি প্রোটন একই গতিশক্তি নিয়ে একটি সুষম চৌম্বক ক্ষেত্রে লম্বভাবে প্রবেশ করল। তাদের বৃত্তাকার পথের ব্যাসার্ধের অনুপাত $r_lpha : r_p$ কত?</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>##PRESET:magnetic-field-wire[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 12)।</t>
+          <t>ব্যাসার্ধ $r = \frac{m v}{q B} = \frac{\sqrt{2m K}}{q B} \propto \frac{\sqrt{m}}{q}$। অনুপাত $\frac{r_\alpha}{r_p} = \frac{\sqrt{m_\alpha}}{\sqrt{m_p}}\frac{q_p}{q_\alpha}$। আমরা জানি $m_\alpha \approx 4 m_p$ এবং $q_\alpha = 2 q_p$। ফলে $\frac{r_\alpha}{r_p} = \frac{\sqrt{4}}{1} \times \frac{1}{2} = \frac{2}{2} = 1$। অর্থাৎ উভয়ের কক্ষপথের ব্যাসার্ধ ঠিক সমান হবে।</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 12</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>$r_\alpha : r_p = 1 : 1 = 1.0$</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4291,38 +4042,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>চৌম্বক ক্ষেত্রে গতিশীল আধানের ওপর লরেন্টজ বল (সমস্যা 13)</t>
+          <t>লরেঞ্জ বল, সাইক্লোট্রন ও তারের ওপর চৌম্বক বল (Lorentz Force &amp; Cyclotron)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[সমস্যা 13: চৌম্বক ক্ষেত্রে গতিশীল আধানের ওপর লরেন্টজ বল]
-একটি প্রোটন ($q = 1.6 \times 10^{-19}\text{ C}$) $B = 0.4\text{ T}$ সুষম চৌম্বক ক্ষেত্রের সাথে লম্বভাবে $v = 10 \times 10^6\text{ m/s}$ বেগে প্রবেশ করল। প্রোটনটির ওপর ক্রিয়াশীল বল এবং এর বৃত্তাকার কক্ষপথের ব্যাসার্ধ কত? ($m = 1.67 \times 10^{-27}\text{ kg}$)</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি কণা যার আধান $q = -4.0\text{ }\mu	ext{C}$ এবং বেগ $ec{v} = (2\hat{i} + 3\hat{j})	imes 10^5	ext{ m/s}$ একটি সুষম চৌম্বক ক্ষেত্র $ec{B} = (0.2\hat{i} - 0.4\hat{k})	ext{ T}$-এ গতিশীল। কণাটির ওপর প্রযুক্ত লরেঞ্জ বলের ভেক্টর রূপ $ec{F}$ এবং এর পরম মান কত?</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 13)।</t>
+          <t>$\vec{v} \times \vec{B} = \begin{vmatrix} \hat{i} &amp; \hat{j} &amp; \hat{k} \\ 2\times 10^5 &amp; 3\times 10^5 &amp; 0 \\ 0.2 &amp; 0 &amp; -0.4 \end{vmatrix} = \hat{i}(-1.2\times 10^5) - \hat{j}(-0.8\times 10^5) + \hat{k}(0 - 0.6\times 10^5) = (-1.2\hat{i} + 0.8\hat{j} - 0.6\hat{k})\times 10^5\text{ T}\cdot\text{m/s}$। বল $\vec{F} = q(\vec{v} \times \vec{B}) = (-4.0 \times 10^{-6}) \times (-1.2\hat{i} + 0.8\hat{j} - 0.6\hat{k})\times 10^5 = 4.8\hat{i} - 3.2\hat{j} + 2.4\hat{k}\text{ N}$। মান $F = \sqrt{4.8^2 + (-3.2)^2 + 2.4^2} = \sqrt{23.04 + 10.24 + 5.76} = \sqrt{39.04} \approx 6.248\text{ N}$।</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 13</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>$\vec{F} = (4.8\hat{i} - 3.2\hat{j} + 2.4\hat{k})\text{ N}$, মান $F = 6.25\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4342,7 +4093,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>সোলেনয়েডের অক্ষীয় চৌম্বক প্রাবল্য (সমস্যা 14)</t>
+          <t>লরেঞ্জ বল, সাইক্লোট্রন ও তারের ওপর চৌম্বক বল (Lorentz Force &amp; Cyclotron)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4355,25 +4106,25 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[সমস্যা 14: সোলেনয়েডের অক্ষীয় চৌম্বক প্রাবল্য]
-$L = 0.6\text{ m}$ দীর্ঘ এবং $N = 1300$ পাকবিশিষ্ট একটি সোলেনয়েডের মধ্য দিয়ে $I = 4.0\text{ A}$ প্রবাহ চালনা করা হলে সোলেনয়েডের অভ্যন্তরে অক্ষীয় চৌম্বক আবেশ $B = \mu_0 n I$ কত টেসলা হবে?</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+দুটি দীর্ঘ সমান্তরাল তারের মধ্যবর্তী দূরত্ব $d = 10\text{ cm}$। প্রতিটি তারের দৈর্ঘ্য $2.0\text{ m}$ এবং উভয়ের মধ্য দিয়ে বিপরীত অভিমুখে $5.0\text{ A}$ কারেন্ট চলছে। তার দুটির প্রতি একক দৈর্ঘ্যে প্রযুক্ত বল এবং সম্পূর্ণ দৈর্ঘ্যে মোট বলের মান ও প্রকৃতি নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 14)।</t>
+          <t>বিপরীতমুখী প্রবাহ পরস্পরকে বিকর্ষণ করে। প্রতি একক দৈর্ঘ্যে বল: $\frac{F}{L} = \frac{\mu_0 I_1 I_2}{2\pi d} = \frac{(2 \times 10^{-7}) \times (5.0 \times 5.0)}{0.10} = \frac{5.0 \times 10^{-6}}{0.10} = 5.0 \times 10^{-5}\text{ N/m}$। $2.0\text{ m}$ দৈর্ঘ্যে মোট বল $F = (5.0 \times 10^{-5}) \times 2.0 = 1.0 \times 10^{-4}\text{ N}$ (বিকর্ষণধর্মী)।</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 14</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>একক দৈর্ঘ্যে বল $\frac{F}{L} = 5.0 \times 10^{-5}\text{ N/m}$, মোট বিকর্ষণ বল $F = 1.0 \times 10^{-4}\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4393,38 +4144,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>সমান্তরাল পরিবাহী তারদ্বয়ের পারস্পরিক বল (সমস্যা 15)</t>
+          <t>লরেঞ্জ বল, সাইক্লোট্রন ও তারের ওপর চৌম্বক বল (Lorentz Force &amp; Cyclotron)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[সমস্যা 15: সমান্তরাল পরিবাহী তারদ্বয়ের পারস্পরিক বল]
-পরস্পর হতে $d = 8\text{ cm}$ দূরত্বে অবস্থিত দুটি সমান্তরাল পরিবাহী তারের মধ্য দিয়ে যথাক্রমে $I_1 = 1\text{ A}$ এবং $I_2 = 15\text{ A}$ বিদ্যুৎ একই দিকে প্রবাহিত হচ্ছে। তার দুটির প্রতি মিটার দৈর্ঘ্যে আকর্ষণ বলের মান কত?</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+বেগ নির্বাচক (Velocity Selector): একটি অঞ্চলে সুষম তড়িৎ ক্ষেত্র $E = 2.0 \times 10^4\text{ V/m}$ এবং সুষম চৌম্বক ক্ষেত্র $B = 0.40\text{ T}$ পরস্পর লম্বভাবে ক্রিয়াশীল। এই অঞ্চলের মধ্য দিয়ে কোনো বিচ্যুতি না ঘটে সরাসরি সরলরেখায় চলে যেতে পারে এমন আহিত কণার বেগ $v$ কত হতে হবে?</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 15)।</t>
+          <t>বিচ্যুতি না হওয়ার শর্তে তড়িৎ বল ও চৌম্বক বল সমান ও বিপরীতমুখী: $q E = q v B \implies v = \frac{E}{B} = \frac{2.0 \times 10^4\text{ V/m}}{0.40\text{ T}} = 5.0 \times 10^4\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 15</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>কণার বেগ $v = 5.0 \times 10^4\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4444,7 +4195,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>তড়িৎবাহী কুণ্ডলীর ওপর প্রযুক্ত টর্ক (সমস্যা 16)</t>
+          <t>লরেঞ্জ বল, সাইক্লোট্রন ও তারের ওপর চৌম্বক বল (Lorentz Force &amp; Cyclotron)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4457,25 +4208,25 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[সমস্যা 16: তড়িৎবাহী কুণ্ডলীর ওপর প্রযুক্ত টর্ক]
-একটি $N = 100$ পাকের আয়তাকার কুণ্ডলীর দৈর্ঘ্য $10\text{ cm}$ ও প্রস্থ $5\text{ cm}$। কুণ্ডলীটির মধ্য দিয়ে $I = 2\text{ A}$ প্রবাহ চলছে এবং এটি $B = 0.4\text{ T}$ চৌম্বক ক্ষেত্রের সাথে সমান্তরালে স্থাপিত। কুণ্ডলীটির ওপর প্রযুক্ত টর্ক $\tau = NIAB$ কত?</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি আয়তাকার তারের কুণ্ডলীর দৈর্ঘ্য $a = 12\text{ cm}$, প্রস্থ $b = 8\text{ cm}$ এবং পাকসংখ্যা $N = 50$। কুণ্ডলীতে $I = 2.0\text{ A}$ তড়িৎ প্রবাহিত হচ্ছে। কুণ্ডলীটির চৌম্বক ভ্রামক $M$ কত? এটিকে $B = 0.50\text{ T}$ সুষম চৌম্বক ক্ষেত্রের সমান্তরালে রাখলে কুণ্ডলীর ওপর প্রযুক্ত সর্বোচ্চ টর্ক $\tau_{\max}$ কত?</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 16)।</t>
+          <t>ক্ষেত্রফল $A = 0.12 \times 0.08 = 0.0096\text{ m}^2$। চৌম্বক ভ্রামক $M = N I A = 50 \times 2.0 \times 0.0096 = 0.96\text{ A}\cdot\text{m}^2$ (বা $\text{J/T}$)। কুণ্ডলীর তল চৌম্বক ক্ষেত্রের সমান্তরাল হলে ক্ষেত্র ভেক্টর $\vec{A}$ ক্ষেত্রের সাথে $90^\circ$ কোণ করে। সর্বোচ্চ টর্ক $\tau_{\max} = M B \sin 90^\circ = 0.96 \times 0.50 = 0.48\text{ N}\cdot\text{m}$।</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 16</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>চৌম্বক ভ্রামক $M = 0.96\text{ A}\cdot\text{m}^2$, সর্বোচ্চ টর্ক $\tau_{\max} = 0.48\text{ N}\cdot\text{m}$</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4495,38 +4246,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>সাইক্লোট্রন কম্পাঙ্ক ও পর্যায়কাল (সমস্যা 17)</t>
+          <t>লরেঞ্জ বল, সাইক্লোট্রন ও তারের ওপর চৌম্বক বল (Lorentz Force &amp; Cyclotron)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[সমস্যা 17: সাইক্লোট্রন কম্পাঙ্ক ও পর্যায়কাল]
-$B = 12.0\text{ T}$ চৌম্বক ক্ষেত্রে একটি ইলেকট্রন বৃত্তাকার কক্ষপথে আবর্তন করছে। ইলেকট্রনটির সাইক্লোট্রন কম্পাঙ্ক ($f = \frac{qB}{2\pi m}$) কত মেগাহার্টজ (MHz) হবে?</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি চলকুণ্ডলী গ্যালভানোমিটারের কুণ্ডলীর ক্ষেত্রফল $A = 4.0\text{ cm}^2$, পাকসংখ্যা $N = 200$, এবং কুণ্ডলীটি $B = 0.25\text{ T}$ রেডিয়াল চৌম্বক ক্ষেত্রে অবস্থিত। ঝুলন তারের মোচড় ধ্রুবক $C = 2.0 \times 10^{-8}\text{ N}\cdot\text{m/rad}$ হলে গ্যালভানোমিটারটির প্রবাহ সংবেদনশীলতা (Current sensitivity $S_i$) কত rad/A?</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 17)।</t>
+          <t>রেডিয়াল ক্ষেত্রে সাম্যাবস্থায় $N I A B = C \theta \implies S_i = \frac{\theta}{I} = \frac{N A B}{C}$। ক্ষেত্রফল $A = 4.0 \times 10^{-4}\text{ m}^2$। $S_i = \frac{200 \times (4.0 \times 10^{-4}) \times 0.25}{2.0 \times 10^{-8}} = \frac{0.020}{2.0 \times 10^{-8}} = 1.0 \times 10^6\text{ rad/A}$।</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 17</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>প্রবাহ সংবেদনশীলতা $S_i = 1.0 \times 10^6\text{ rad/A}$</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4546,7 +4297,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ভূ-চৌম্বকত্বের আনুভূমিক উপাংশ ও বিনতি কোণ (সমস্যা 18)</t>
+          <t>লরেঞ্জ বল, সাইক্লোট্রন ও তারের ওপর চৌম্বক বল (Lorentz Force &amp; Cyclotron)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4559,25 +4310,25 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[সমস্যা 18: ভূ-চৌম্বকত্বের আনুভূমিক উপাংশ ও বিনতি কোণ]
-কোনো স্থানে পৃথিবীর মোট চৌম্বক ক্ষেত্রের মান $B = 4 \times 10^{-5}\text{ T}$ এবং বিনতি কোণ $\delta = 20^\circ$। ঐ স্থানে ভূ-চৌম্বক ক্ষেত্রের আনুভূমিক উপাংশ ($B_H = B\cos\delta$) এবং উলম্ব উপাংশ ($B_V$) কত?</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ইলেকট্রন $v = 1.0 \times 10^7\text{ m/s}$ বেগে একটি সুষম চৌম্বক ক্ষেত্র $B = 0.10\text{ T}$-এর সাথে $	heta = 30^\circ$ কোণে প্রবেশ করল। ইলেকট্রনটির হেলিকাল পথের ব্যাসার্ধ $r$ এবং স্পাইরাল ধাপের ব্যবধান (Pitch $p$) নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 18)।</t>
+          <t>লম্ব বেগ উপাংশ $v_\perp = v\sin 30^\circ = 0.5 \times 10^7\text{ m/s}$। সমান্তরাল উপাংশ $v_\parallel = v\cos 30^\circ = 0.866 \times 10^7\text{ m/s}$। ব্যাসার্ধ $r = \frac{m v_\perp}{e B} = \frac{(9.11 \times 10^{-31}) \times (5.0 \times 10^6)}{(1.6 \times 10^{-19}) \times 0.10} = \frac{4.555 \times 10^{-24}}{1.6 \times 10^{-20}} \approx 2.847 \times 10^{-4}\text{ m} \approx 0.285\text{ mm}$। পর্যায়কাল $T = \frac{2\pi m}{e B} = \frac{2\pi (9.11 \times 10^{-31})}{1.6 \times 10^{-20}} \approx 3.577 \times 10^{-10}\text{ s}$। পিচ $p = v_\parallel T = (8.66 \times 10^6) \times (3.577 \times 10^{-10}) \approx 3.098 \times 10^{-3}\text{ m} = 3.10\text{ mm}$।</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 18</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>হেলিক্সের ব্যাসার্ধ $r = 0.285\text{ mm}$, পিচ $p = 3.10\text{ mm}$</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4597,38 +4348,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>অ্যাম্পিয়ারের চক্রীয় সূত্র ও টরয়েড (সমস্যা 19)</t>
+          <t>লরেঞ্জ বল, সাইক্লোট্রন ও তারের ওপর চৌম্বক বল (Lorentz Force &amp; Cyclotron)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[সমস্যা 19: অ্যাম্পিয়ারের চক্রীয় সূত্র ও টরয়েড]
-একটি টরয়েডের গড় ব্যাসার্ধ $R = 40\text{ cm}$ এবং মোট পাকসংখ্যা $N = 13000$। এর মধ্য দিয়ে $I = 3\text{ A}$ তড়িৎ প্রবাহিত হলে টরয়েডের অভ্যন্তরে চৌম্বক ক্ষেত্রের মান কত?</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=1.5][size:small]##
+একটি সোজা তারের ভর $m = 20\text{ g}$ এবং দৈর্ঘ্য $L = 50\text{ cm}$। তারটিতে তড়িৎ প্রবাহিত করে একটি অনুভূমিক সুষম চৌম্বক ক্ষেত্র $B = 0.20\text{ T}$-এর মধ্যে অভিকর্ষের বিপরীতে শূন্যে ঝুলিয়ে রাখতে হলে তারে কত অ্যাম্পিয়ার তড়িৎ পাঠাতে হবে? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 19)।</t>
+          <t>চৌম্বক ঊর্ধ্বমুখী বল তারের ওজনকে ভারসাম্য করে: $I L B = m g \implies I = \frac{m g}{L B} = \frac{(0.020\text{ kg}) \times 9.8}{(0.50\text{ m}) \times (0.20\text{ T})} = \frac{0.196}{0.10} = 1.96\text{ A}$।</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 19</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>প্রয়োজনীয় কারেন্ট $I = 1.96\text{ A}$</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4648,7 +4399,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>চৌম্বক ভ্রামক ও পরমাণুর বোর ম্যাগনেটন (সমস্যা 20)</t>
+          <t>লরেঞ্জ বল, সাইক্লোট্রন ও তারের ওপর চৌম্বক বল (Lorentz Force &amp; Cyclotron)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4661,25 +4412,25 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[সমস্যা 20: চৌম্বক ভ্রামক ও পরমাণুর বোর ম্যাগনেটন]
-একটি বৃত্তাকার হাইড্রোজেন কক্ষপথে ইলেকট্রন প্রতি সেকেন্ডে $f = 6 \times 10^{15}$ বার ঘোরে। কক্ষপথের ব্যাসার্ধ $r = 0.53\text{ \AA}$ হলে এর সমতুল্য চৌম্বক দ্বিমেরু ভ্রামক ($M = I A$) কত?</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+হল ক্রিয়া (Hall Effect): একটি $w = 1.0\text{ cm}$ চওড়া এবং $t = 1.0\text{ mm}$ পুরু ধাতব পাতে $I = 20\text{ A}$ কারেন্ট চলছে। পাতের তলের লম্বভাবে $B = 1.5\text{ T}$ চৌম্বক ক্ষেত্র প্রয়োগ করায় পাতের দুই প্রান্তে $V_H = 1.5\text{ }\mu	ext{V}$ হল ভোল্টেজ উৎপন্ন হলো। পরিবাহীর মুক্ত ইলেকট্রন ঘনত্ব $n$ কত?</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 20)।</t>
+          <t>হল ভোল্টেজের সমীকরণ: $V_H = \frac{I B}{n t e} \implies n = \frac{I B}{t e V_H}$। মান বসিয়ে: $n = \frac{20 \times 1.5}{(1.0 \times 10^{-3}) \times (1.6 \times 10^{-19}) \times (1.5 \times 10^{-6})} = \frac{30}{2.4 \times 10^{-28}} = 1.25 \times 10^{29}\text{ m}^{-3}$।</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 20</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>মুক্ত ইলেকট্রন ঘনত্ব $n = 1.25 \times 10^{29}\text{ m}^{-3}$</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4699,44 +4450,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>বৃত্তাকার কুণ্ডলীর কেন্দ্রে চৌম্বক ক্ষেত্র (সমস্যা 21)</t>
+          <t>ভূ-চুম্বকত্ব ও চৌম্বক পদার্থের ধর্ম (Earth Magnetism &amp; Materials)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>##PRESET:solenoid[size:medium]##
-[সমস্যা 21: বৃত্তাকার কুণ্ডলীর কেন্দ্রে চৌম্বক ক্ষেত্র]
-##PRESET:solenoid[size:medium]##
-$N = 800$ পাকসংখ্যা এবং $R = 4\text{ cm}$ ব্যাসার্ধবিশিষ্ট একটি সমতল বৃত্তাকার তারকুণ্ডলীতে $I = 2.5\text{ A}$ বিদ্যুৎ প্রবাহিত হচ্ছে। কুণ্ডলীর কেন্দ্রে চৌম্বক ক্ষেত্রের মান কত? ($\mu_0 = 4\pi \times 10^{-7}\text{ T}\cdot\text{m/A}$)</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+কোনো স্থানে পৃথিবীর মোট চৌম্বক ক্ষেত্র $B = 4.0 \times 10^{-5}\text{ T}$ এবং বিনতি কোণ (Angle of dip) $\delta = 60^\circ$। ওই স্থানের ভূ-চৌম্বক ক্ষেত্রের অনুভূমিক উপাংশ $B_H$ এবং উল্লম্ব উপাংশ $B_V$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>##PRESET:solenoid[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 21)।</t>
+          <t>অনুভূমিক উপাংশ $B_H = B \cos\delta = (4.0 \times 10^{-5})\cos 60^\circ = (4.0 \times 10^{-5})(0.5) = 2.0 \times 10^{-5}\text{ T}$। উল্লম্ব উপাংশ $B_V = B \sin\delta = (4.0 \times 10^{-5})\sin 60^\circ = (4.0 \times 10^{-5}) \times \frac{\sqrt{3}}{2} \approx 3.464 \times 10^{-5}\text{ T}$।</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 21</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>$B_H = 2.0 \times 10^{-5}\text{ T}, B_V = 3.464 \times 10^{-5}\text{ T}$</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4756,7 +4501,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>দীর্ঘ ঋজু পরিবাহী ও বায়োট-স্যাভার্ট সূত্র (সমস্যা 22)</t>
+          <t>ভূ-চুম্বকত্ব ও চৌম্বক পদার্থের ধর্ম (Earth Magnetism &amp; Materials)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4769,31 +4514,25 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>##PRESET:magnetic-field-wire[size:medium]##
-[সমস্যা 22: দীর্ঘ ঋজু পরিবাহী ও বায়োট-স্যাভার্ট সূত্র]
-##PRESET:magnetic-field-wire[size:medium]##
-একটি সোজা দীর্ঘ পরিবাহী তারের মধ্য দিয়ে $I = 100\text{ A}$ তড়িৎ প্রবাহিত হচ্ছে। তারটি হতে $d = 7\text{ cm}$ লম্ব দূরত্বে চৌম্বক ক্ষেত্রের মান কত টেসলা?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি স্থানে ভূ-চৌম্বক ক্ষেত্রের অনুভূমিক ও উল্লম্ব উপাংশ সমান ($B_H = B_V$)। ওই স্থানের বিনতি কোণ কত? চৌম্বক বিষুবরেখায় (Magnetic Equator) এবং চৌম্বক মেরুতে (Magnetic Pole) বিনতি কোণ যথাক্রমে কত হয়?</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>##PRESET:magnetic-field-wire[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 22)।</t>
+          <t>বিনতি কোণের সম্পর্ক: $\tan\delta = \frac{B_V}{B_H}$। $B_H = B_V$ হলে $\tan\delta = 1 \implies \delta = 45^\circ$। বিষুবরেখায় উল্লম্ব উপাংশ থাকে না ($B_V = 0 \implies \delta = 0^\circ$)। মেরুতে অনুভূমিক উপাংশ থাকে না ($B_H = 0 \implies \tan\delta = \infty \implies \delta = 90^\circ$)।</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 22</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>বিনতি কোণ $\delta = 45^\circ$, বিষুবরেখায় $\delta = 0^\circ$, মেরুতে $\delta = 90^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4813,38 +4552,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>চৌম্বক ক্ষেত্রে গতিশীল আধানের ওপর লরেন্টজ বল (সমস্যা 23)</t>
+          <t>ভূ-চুম্বকত্ব ও চৌম্বক পদার্থের ধর্ম (Earth Magnetism &amp; Materials)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[সমস্যা 23: চৌম্বক ক্ষেত্রে গতিশীল আধানের ওপর লরেন্টজ বল]
-একটি প্রোটন ($q = 1.6 \times 10^{-19}\text{ C}$) $B = 0.12\text{ T}$ সুষম চৌম্বক ক্ষেত্রের সাথে লম্বভাবে $v = 10 \times 10^6\text{ m/s}$ বেগে প্রবেশ করল। প্রোটনটির ওপর ক্রিয়াশীল বল এবং এর বৃত্তাকার কক্ষপথের ব্যাসার্ধ কত? ($m = 1.67 \times 10^{-27}\text{ kg}$)</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>##GEO:triangle[b=3,h=3][size:small]##
+একটি স্থান হতে আপাত বিনতি কোণ পরিমাপে একটি উলম্ব তলে আপাত বিনতি পাওয়া গেল $\delta_1 = 30^\circ$ এবং এর সাথে সমকোণে অবস্থিত অপর একটি তলে আপাত বিনতি $\delta_2 = 45^\circ$। স্থানটির প্রকৃত বিনতি কোণ $\delta$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>##GEO:triangle[b=3,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 23)।</t>
+          <t>আপাত বিনতির সার্বজনীন সমীকরণ: $\cot^2\delta = \cot^2\delta_1 + \cot^2\delta_2$। মান বসিয়ে: $\cot^2\delta = (\cot 30^\circ)^2 + (\cot 45^\circ)^2 = (\sqrt{3})^2 + 1^2 = 3 + 1 = 4$। অতএব $\cot\delta = 2 \implies \tan\delta = \frac{1}{2} = 0.50 \implies \delta = \arctan(0.50) \approx 26.565^\circ \approx 26.57^\circ$।</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 23</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>প্রকৃত বিনতি কোণ $\delta = 26.57^\circ$ ($\cot^2\delta = \cot^2\delta_1 + \cot^2\delta_2$)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4864,7 +4603,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>সোলেনয়েডের অক্ষীয় চৌম্বক প্রাবল্য (সমস্যা 24)</t>
+          <t>ভূ-চুম্বকত্ব ও চৌম্বক পদার্থের ধর্ম (Earth Magnetism &amp; Materials)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4877,25 +4616,25 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[সমস্যা 24: সোলেনয়েডের অক্ষীয় চৌম্বক প্রাবল্য]
-$L = 0.2\text{ m}$ দীর্ঘ এবং $N = 1300$ পাকবিশিষ্ট একটি সোলেনয়েডের মধ্য দিয়ে $I = 4.0\text{ A}$ প্রবাহ চালনা করা হলে সোলেনয়েডের অভ্যন্তরে অক্ষীয় চৌম্বক আবেশ $B = \mu_0 n I$ কত টেসলা হবে?</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি চৌম্বক পদার্থের আপেক্ষিক প্রবেশ্যতা $\mu_r = 1500$। পদার্থটির চৌম্বক গ্রাহিতা (Magnetic susceptibility $\chi_m$) কত এবং পদার্থটি কোন প্রকৃতির?</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 24)।</t>
+          <t>সম্পর্ক: $\mu_r = 1 + \chi_m \implies \chi_m = \mu_r - 1 = 1500 - 1 = 1499.0$। যেহেতু $\chi_m \gg 1$ (অত্যন্ত উচ্চ ধনাত্মক মান), তাই পদার্থটি ফেরোচৌম্বক পদার্থ।</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 24</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>চৌম্বক গ্রাহিতা $\chi_m = 1499.0$, পদার্থটি তীব্র ফেরোচৌম্বক (Ferromagnetic)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4915,38 +4654,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>সমান্তরাল পরিবাহী তারদ্বয়ের পারস্পরিক বল (সমস্যা 25)</t>
+          <t>ভূ-চুম্বকত্ব ও চৌম্বক পদার্থের ধর্ম (Earth Magnetism &amp; Materials)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[সমস্যা 25: সমান্তরাল পরিবাহী তারদ্বয়ের পারস্পরিক বল]
-পরস্পর হতে $d = 4\text{ cm}$ দূরত্বে অবস্থিত দুটি সমান্তরাল পরিবাহী তারের মধ্য দিয়ে যথাক্রমে $I_1 = 1\text{ A}$ এবং $I_2 = 15\text{ A}$ বিদ্যুৎ একই দিকে প্রবাহিত হচ্ছে। তার দুটির প্রতি মিটার দৈর্ঘ্যে আকর্ষণ বলের মান কত?</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি পরমাণুতে একটি ইলেকট্রন ($e = 1.6 \times 10^{-19}\text{ C}$) $r = 5.3 \times 10^{-11}\text{ m}$ ব্যাসার্ধের বৃত্তাকার কক্ষপথে $v = 2.2 \times 10^6\text{ m/s}$ বেগে ঘুরছে। ইলেকট্রনটির কক্ষীয় গতির ফলে উৎপন্ন সমতুল্য তড়িৎ প্রবাহ $I$ এবং কক্ষীয় চৌম্বক ভ্রামক (Bohr Magneton অনুসারী) নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 25)।</t>
+          <t>পর্যায়কাল $T = \frac{2\pi r}{v} = \frac{2\pi (5.3 \times 10^{-11})}{2.2 \times 10^6} \approx 1.5136 \times 10^{-16}\text{ s}$। সমতুল্য প্রবাহ $I = \frac{e}{T} = \frac{1.6 \times 10^{-19}}{1.5136 \times 10^{-16}} \approx 1.057 \times 10^{-3}\text{ A} = 1.057\text{ mA}$। ক্ষেত্রফল $A = \pi r^2 = \pi (5.3 \times 10^{-11})^2 \approx 8.825 \times 10^{-21}\text{ m}^2$। চৌম্বক ভ্রামক $M = I A = (1.057 \times 10^{-3}) \times (8.825 \times 10^{-21}) \approx 9.328 \times 10^{-24}\text{ A}\cdot\text{m}^2 \approx 1.0\\text{ Bohr magneton}$।</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 25</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>সমতুল্য কারেন্ট $I = 1.057\text{ mA}$, চৌম্বক ভ্রামক $M = 9.32 \times 10^{-24}\text{ A}\cdot\text{m}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4966,7 +4705,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>তড়িৎবাহী কুণ্ডলীর ওপর প্রযুক্ত টর্ক (সমস্যা 26)</t>
+          <t>ভূ-চুম্বকত্ব ও চৌম্বক পদার্থের ধর্ম (Earth Magnetism &amp; Materials)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4979,25 +4718,25 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[সমস্যা 26: তড়িৎবাহী কুণ্ডলীর ওপর প্রযুক্ত টর্ক]
-একটি $N = 60$ পাকের আয়তাকার কুণ্ডলীর দৈর্ঘ্য $10\text{ cm}$ ও প্রস্থ $5\text{ cm}$। কুণ্ডলীটির মধ্য দিয়ে $I = 2\text{ A}$ প্রবাহ চলছে এবং এটি $B = 0.4\text{ T}$ চৌম্বক ক্ষেত্রের সাথে সমান্তরালে স্থাপিত। কুণ্ডলীটির ওপর প্রযুক্ত টর্ক $\tau = NIAB$ কত?</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=1.5][size:small]##
+একটি দণ্ড চুম্বকের দৈর্ঘ্য $2l = 10.0\text{ cm}$ এবং মেরু শক্তি $m = 20.0\text{ A}\cdot	ext{m}$। চুম্বকটির চৌম্বক ভ্রামক $M$ কত? চুম্বকের মধ্যবিন্দু হতে অক্ষীয় অবস্থানে $25.0\text{ cm}$ দূরে চৌম্বক ক্ষেত্র কত? ($\mu_0 = 4\pi \times 10^{-7}\text{ T}\cdot\text{m/A}$)।</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 26)।</t>
+          <t>চৌম্বক ভ্রামক $M = m(2l) = 20.0 \times 0.10 = 2.0\text{ A}\cdot\text{m}^2$। অক্ষীয় চৌম্বক ক্ষেত্র $B = \frac{\mu_0}{4\pi}\frac{2M d}{(d^2 - l^2)^2}$। $d = 0.25\text{ m}, l = 0.05\text{ m}$। $d^2 - l^2 = 0.0625 - 0.0025 = 0.060\text{ m}^2$। $(d^2 - l^2)^2 = 0.0036$। $B = (10^{-7}) \times \frac{2(2.0)(0.25)}{0.0036} = \frac{1.0 \times 10^{-7}}{0.0036} \approx 2.778 \times 10^{-5}\text{ T}$ (বা দূরবর্তী সন্নিকর্ষে $\frac{2kM}{d^3} = \frac{2 \times 10^{-7} \times 2}{0.015625} \approx 2.56 \times 10^{-5}\text{ T}$)।</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 26</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>চৌম্বক ভ্রামক $M = 2.0\text{ A}\cdot\text{m}^2$, অক্ষীয় চৌম্বক ক্ষেত্র $B = 2.96 \times 10^{-5}\text{ T}$</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5017,38 +4756,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>সাইক্লোট্রন কম্পাঙ্ক ও পর্যায়কাল (সমস্যা 27)</t>
+          <t>ভূ-চুম্বকত্ব ও চৌম্বক পদার্থের ধর্ম (Earth Magnetism &amp; Materials)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[সমস্যা 27: সাইক্লোট্রন কম্পাঙ্ক ও পর্যায়কাল]
-$B = 8.0\text{ T}$ চৌম্বক ক্ষেত্রে একটি ইলেকট্রন বৃত্তাকার কক্ষপথে আবর্তন করছে। ইলেকট্রনটির সাইক্লোট্রন কম্পাঙ্ক ($f = \frac{qB}{2\pi m}$) কত মেগাহার্টজ (MHz) হবে?</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি চৌম্বক পদার্থের কিউরি তাপমাত্রা $T_c = 1043\text{ K}$ (লোহা)। কিউরি-ওয়েইস সূত্র $\chi = rac{C}{T - T_c}$ অনুসারে $1200\text{ K}$ তাপমাত্রায় লোহার চৌম্বক গ্রাহিতা $1100\text{ K}$ তাপমাত্রার গ্রাহিতার শতকরা কত অংশ হবে?</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 27)।</t>
+          <t>কিউরি তাপমাত্রার উপরে পদার্থটি প্যারাচৌম্বক আচরণ করে: $\chi \propto \frac{1}{T - T_c}$। $\chi_{1100} \propto \frac{1}{1100 - 1043} = \frac{1}{57}$। $\chi_{1200} \propto \frac{1}{1200 - 1043} = \frac{1}{157}$। অনুপাত $\frac{\chi_{1200}}{\chi_{1100}} = \frac{57}{157} \approx 0.36306 \approx 36.31\%$।</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 27</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>গ্রাহিতার অনুপাত $\frac{\chi_{1200}}{\chi_{1100}} = 0.3636$ ($36.36\%$ অংশে নেমে আসবে)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5068,7 +4807,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ভূ-চৌম্বকত্বের আনুভূমিক উপাংশ ও বিনতি কোণ (সমস্যা 28)</t>
+          <t>ভূ-চুম্বকত্ব ও চৌম্বক পদার্থের ধর্ম (Earth Magnetism &amp; Materials)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5081,25 +4820,25 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[সমস্যা 28: ভূ-চৌম্বকত্বের আনুভূমিক উপাংশ ও বিনতি কোণ]
-কোনো স্থানে পৃথিবীর মোট চৌম্বক ক্ষেত্রের মান $B = 4 \times 10^{-5}\text{ T}$ এবং বিনতি কোণ $\delta = 100^\circ$। ঐ স্থানে ভূ-চৌম্বক ক্ষেত্রের আনুভূমিক উপাংশ ($B_H = B\cos\delta$) এবং উলম্ব উপাংশ ($B_V$) কত?</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=1.5][size:small]##
+একটি অনুভূমিক সমতলে রাখা একটি চৌম্বক শলাকার দোলনকাল $T_1 = 2.0\text{ s}$ যেখানে $B_H = 3.0 \times 10^{-5}\text{ T}$। অন্য একটি স্থানে যেখানে $B_H' = 1.2 \times 10^{-5}\text{ T}$, সেখানে একই শলাকার দোলনকাল কত হবে?</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 28)।</t>
+          <t>কম্পন ম্যাগনেটোমিটারের সূত্র: $T = 2\pi\sqrt{\frac{I}{M B_H}} \propto \frac{1}{\sqrt{B_H}}$। $\frac{T_2}{T_1} = \sqrt{\frac{B_H}{B_H'}} = \sqrt{\frac{3.0 \times 10^{-5}}{1.2 \times 10^{-5}}} = \sqrt{2.5} \approx 1.5811$। নতুন দোলনকাল $T_2 = 2.0 \times 1.5811 \approx 3.162\text{ s}$।</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 28</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>নতুন দোলনকাল $T_2 = 3.16\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5119,38 +4858,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>অ্যাম্পিয়ারের চক্রীয় সূত্র ও টরয়েড (সমস্যা 29)</t>
+          <t>ভূ-চুম্বকত্ব ও চৌম্বক পদার্থের ধর্ম (Earth Magnetism &amp; Materials)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[সমস্যা 29: অ্যাম্পিয়ারের চক্রীয় সূত্র ও টরয়েড]
-একটি টরয়েডের গড় ব্যাসার্ধ $R = 120\text{ cm}$ এবং মোট পাকসংখ্যা $N = 13000$। এর মধ্য দিয়ে $I = 3\text{ A}$ তড়িৎ প্রবাহিত হলে টরয়েডের অভ্যন্তরে চৌম্বক ক্ষেত্রের মান কত?</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি লোহার দণ্ডের আয়তন $V = 1.0 	imes 10^{-4}\text{ m}^3$। দণ্ডটিকে $50\text{ Hz}$ কম্পাঙ্কের এসি চৌম্বক ক্ষেত্রে চুম্বকিত করায় হিস্টেরেসিস লুপের প্রতি চক্রের শক্তি অপচয় ঘনত্ব $200\text{ J/m}^3$। প্রতি সেকেন্ডে লোহাটিতে উৎপন্ন হিস্টেরেসিস তাপ শক্তি কত ওয়াট?</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 29)।</t>
+          <t>প্রতি চক্রে মোট শক্তি অপচয় $W_{\text{cycle}} = \text{ক্ষেত্রফল} \times V = (200\text{ J/m}^3) \times (1.0 \times 10^{-4}\text{ m}^3) = 0.020\text{ J}$। প্রতি সেকেন্ডে চক্র সংখ্যা $f = 50\text{ s}^{-1}$। প্রতি সেকেন্ডে অপচয়কৃত ক্ষমতা $P = W_{\text{cycle}} \times f = 0.020 \times 50 = 1.0\text{ W}$।</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 29</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>তাপ উৎপাদন ক্ষমতা $P = 1.0\text{ W}$</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5170,7 +4909,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>চৌম্বক ভ্রামক ও পরমাণুর বোর ম্যাগনেটন (সমস্যা 30)</t>
+          <t>ভূ-চুম্বকত্ব ও চৌম্বক পদার্থের ধর্ম (Earth Magnetism &amp; Materials)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5183,25 +4922,25 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[সমস্যা 30: চৌম্বক ভ্রামক ও পরমাণুর বোর ম্যাগনেটন]
-একটি বৃত্তাকার হাইড্রোজেন কক্ষপথে ইলেকট্রন প্রতি সেকেন্ডে $f = 2 \times 10^{15}$ বার ঘোরে। কক্ষপথের ব্যাসার্ধ $r = 0.53\text{ \AA}$ হলে এর সমতুল্য চৌম্বক দ্বিমেরু ভ্রামক ($M = I A$) কত?</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+ডায়াচৌম্বক, প্যারাচৌম্বক ও ফেরোচৌম্বক পদার্থের চৌম্বক গ্রাহিতার চিহ্নের তুলনা: এদের চৌম্বক গ্রাহিতা $\chi_m$ যথাক্রমে ধনাত্মক না ঋণাত্মক এবং তাপমাত্রার ওপর কীভাবে নির্ভরশীল?</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 30)।</t>
+          <t>ডায়াচৌম্বক পদার্থের কোনো স্থায়ী চৌম্বক দ্বিমেরু থাকে না; আবিষ্ট দ্বিমেরু প্রযুক্ত ক্ষেত্রের বিপরীতে সৃষ্টি হয় ফলে $\chi$ ঋণাত্মক ও তাপমাত্রা নিরপেক্ষ। প্যারাচৌম্বক পদার্থে স্থায়ী দ্বিমেরু থাকে যা তাপমাত্রা বৃদ্ধির সাথে সাথে তাপীয় বিশৃঙ্খলার কারণে বিক্ষিপ্ত হয় ($\chi \propto 1/T$)। ফেরোচৌম্বক পদার্থে ডোমেন গঠনের কারণে $\chi$ অত্যন্ত বিশাল ধনাত্মক হয়।</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 30</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>ডায়া: $\chi &lt; 0$ (ক্ষুদ্র ঋণাত্মক, তাপমাত্রা নিরপেক্ষ); প্যারা: $\chi &gt; 0$ (ক্ষুদ্র ধনাত্মক, $\chi \propto 1/T$); ফেরো: $\chi \gg 0$ (বিশাল ধনাত্মক, কিউরি তাপমাত্রার পর প্যারাচৌম্বক)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5221,44 +4960,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>বৃত্তাকার কুণ্ডলীর কেন্দ্রে চৌম্বক ক্ষেত্র (সমস্যা 31)</t>
+          <t>উন্নত চৌম্বক বর্তনী ও কুণ্ডলী বিশ্লেষণ (Advanced Magnetic Circuits)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>##PRESET:solenoid[size:medium]##
-[সমস্যা 31: বৃত্তাকার কুণ্ডলীর কেন্দ্রে চৌম্বক ক্ষেত্র]
-##PRESET:solenoid[size:medium]##
-$N = 400$ পাকসংখ্যা এবং $R = 4\text{ cm}$ ব্যাসার্ধবিশিষ্ট একটি সমতল বৃত্তাকার তারকুণ্ডলীতে $I = 2.5\text{ A}$ বিদ্যুৎ প্রবাহিত হচ্ছে। কুণ্ডলীর কেন্দ্রে চৌম্বক ক্ষেত্রের মান কত? ($\mu_0 = 4\pi \times 10^{-7}\text{ T}\cdot\text{m/A}$)</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি অর্ধবৃত্তাকার পরিবাহী তার যার ব্যাসার্ধ $R = 20\text{ cm}$, একটি সুষম চৌম্বক ক্ষেত্র $B = 0.50\text{ T}$-এর লম্বতলে স্থাপিত। তারটিতে $I = 4.0\text{ A}$ তড়িৎ চললে তারটির ওপর প্রযুক্ত নিট চৌম্বক বল কত?</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>##PRESET:solenoid[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 31)।</t>
+          <t>যেকোনো বক্র পরিবাহীর ওপর নিট বল কেবল প্রান্তদ্বয়ের সরলরেখীয় দূরত্বের সমান সরল তারের ওপর বলের সমান: $L_{\text{eff}} = 2R = 2(0.20) = 0.40\text{ m}$। লব্ধি বল $F = I L_{\text{eff}} B = 4.0 \times 0.40 \times 0.50 = 0.80\text{ N}$।</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 31</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>নিট চৌম্বক বল $F = 0.80\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5278,12 +5011,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>দীর্ঘ ঋজু পরিবাহী ও বায়োট-স্যাভার্ট সূত্র (সমস্যা 32)</t>
+          <t>উন্নত চৌম্বক বর্তনী ও কুণ্ডলী বিশ্লেষণ (Advanced Magnetic Circuits)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -5291,31 +5024,25 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>##PRESET:magnetic-field-wire[size:medium]##
-[সমস্যা 32: দীর্ঘ ঋজু পরিবাহী ও বায়োট-স্যাভার্ট সূত্র]
-##PRESET:magnetic-field-wire[size:medium]##
-একটি সোজা দীর্ঘ পরিবাহী তারের মধ্য দিয়ে $I = 60\text{ A}$ তড়িৎ প্রবাহিত হচ্ছে। তারটি হতে $d = 7\text{ cm}$ লম্ব দূরত্বে চৌম্বক ক্ষেত্রের মান কত টেসলা?</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি ইলেকট্রন $v_0$ বেগে $x$-অক্ষ বরাবর গতিশীল অবস্থায় $x = 0$ হতে $x = d$ অঞ্চলের মধ্যে একটি সুষম চৌম্বক ক্ষেত্র $B\hat{k}$-এ প্রবেশ করল। ইলেকট্রনটি যেন অপর প্রান্ত $x = d$ অতিক্রম করতে না পেরে পুনরায় $x &lt; 0$ অঞ্চলে ফিরে আসে তার জন্য ন্যূনতম চৌম্বক ক্ষেত্র $B_{\min}$ কত হতে হবে?</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>##PRESET:magnetic-field-wire[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 32)।</t>
+          <t>ফিরে আসার শর্ত হলো বৃত্তাকার পথের ব্যাসার্ধ $r \le d$ হতে হবে: $\frac{m v_0}{e B} \le d \implies B \ge \frac{m v_0}{e d}$। সুতরাং ন্যূনতম ক্ষেত্র $B_{\min} = \frac{m v_0}{e d}$।</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 32</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>$B_{\min} = \frac{m v_0}{e d}$</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5335,38 +5062,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>চৌম্বক ক্ষেত্রে গতিশীল আধানের ওপর লরেন্টজ বল (সমস্যা 33)</t>
+          <t>উন্নত চৌম্বক বর্তনী ও কুণ্ডলী বিশ্লেষণ (Advanced Magnetic Circuits)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[সমস্যা 33: চৌম্বক ক্ষেত্রে গতিশীল আধানের ওপর লরেন্টজ বল]
-একটি প্রোটন ($q = 1.6 \times 10^{-19}\text{ C}$) $B = 0.8\text{ T}$ সুষম চৌম্বক ক্ষেত্রের সাথে লম্বভাবে $v = 10 \times 10^6\text{ m/s}$ বেগে প্রবেশ করল। প্রোটনটির ওপর ক্রিয়াশীল বল এবং এর বৃত্তাকার কক্ষপথের ব্যাসার্ধ কত? ($m = 1.67 \times 10^{-27}\text{ kg}$)</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>##GEO:triangle[b=3,h=3][size:small]##
+একটি সমবাহু ত্রিভুজাকার কুণ্ডলী যার বাহু $a = 10\text{ cm}$ এবং প্রবাহ $I = 2.0\text{ A}$। কুণ্ডলীটির চৌম্বক ভ্রামক $M$ কত?</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>##GEO:triangle[b=3,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 33)।</t>
+          <t>সমবাহু ত্রিভুজের ক্ষেত্রফল $A = \frac{\sqrt{3}}{4} a^2 = \frac{\sqrt{3}}{4} (0.10)^2 = \frac{\sqrt{3}}{4} \times 0.01 = 0.0025\sqrt{3} \approx 4.33 \times 10^{-3}\text{ m}^2$। চৌম্বক ভ্রামক $M = I A = 2.0 \times (4.33 \times 10^{-3}) = 8.66 \times 10^{-3}\text{ A}\cdot\text{m}^2$।</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 33</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>চৌম্বক ভ্রামক $M = 8.66 \times 10^{-3}\text{ A}\cdot\text{m}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5386,12 +5113,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>সোলেনয়েডের অক্ষীয় চৌম্বক প্রাবল্য (সমস্যা 34)</t>
+          <t>উন্নত চৌম্বক বর্তনী ও কুণ্ডলী বিশ্লেষণ (Advanced Magnetic Circuits)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -5399,25 +5126,25 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[সমস্যা 34: সোলেনয়েডের অক্ষীয় চৌম্বক প্রাবল্য]
-$L = 0.10\text{ m}$ দীর্ঘ এবং $N = 1300$ পাকবিশিষ্ট একটি সোলেনয়েডের মধ্য দিয়ে $I = 4.0\text{ A}$ প্রবাহ চালনা করা হলে সোলেনয়েডের অভ্যন্তরে অক্ষীয় চৌম্বক আবেশ $B = \mu_0 n I$ কত টেসলা হবে?</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ধনাত্মক আধান $q$ বিশিষ্ট $m$ ভরের কণা অভিকর্ষের অধীনে $h$ উচ্চতা হতে একটি অনুভূমিক সুষম চৌম্বক ক্ষেত্র $B$-এ মুক্তভাবে পড়ল। কণাটির সর্বোচ্চ অনুভূমিক বেগ এবং এর গতিপথের প্রকৃতি কীরূপ হবে?</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 34)।</t>
+          <t>অভিকর্ষ বল নিচের দিকে এবং চৌম্বক বল গতির লম্ব দিকে ক্রিয়া করায় কণাটি সাইক্লয়ডাল বক্ররেখা গঠন করে। এতে কোনো কাজ না হওয়ায় মোট যান্ত্রিক শক্তি সংরক্ষিত থাকে।</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 34</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>কণাটি সাইক্লয়েড (Cycloid) গতিপথ অনুসরণ করবে, উল্লম্ব সাম্যাবস্থায় $v_{\max} = \frac{2mg}{qB}$</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5437,38 +5164,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>সমান্তরাল পরিবাহী তারদ্বয়ের পারস্পরিক বল (সমস্যা 35)</t>
+          <t>উন্নত চৌম্বক বর্তনী ও কুণ্ডলী বিশ্লেষণ (Advanced Magnetic Circuits)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[সমস্যা 35: সমান্তরাল পরিবাহী তারদ্বয়ের পারস্পরিক বল]
-পরস্পর হতে $d = 12\text{ cm}$ দূরত্বে অবস্থিত দুটি সমান্তরাল পরিবাহী তারের মধ্য দিয়ে যথাক্রমে $I_1 = 1\text{ A}$ এবং $I_2 = 15\text{ A}$ বিদ্যুৎ একই দিকে প্রবাহিত হচ্ছে। তার দুটির প্রতি মিটার দৈর্ঘ্যে আকর্ষণ বলের মান কত?</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি পরিবাহী দণ্ডের দৈর্ঘ্য $L = 1.0\text{ m}$ এবং ভর $M = 0.5\text{ kg}$ দুটি নমনীয় পরিবাহী সুতা দ্বারা অনুভূমিকভাবে ঝুলানো আছে। সেখানে অনুভূমিক চৌম্বক ক্ষেত্র $B = 0.49\text{ T}$ লম্বভাবে ক্রিয়াশীল। সুতার টান সম্পূর্ণ শূন্য করতে তারের মধ্য দিয়ে কত অ্যাম্পিয়ার তড়িৎ পাঠাতে হবে?</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 35)।</t>
+          <t>টান শূন্য হওয়ার শর্তে চৌম্বক ঊর্ধ্বমুখী বল সম্পূর্ণ ওজনকে বহন করবে: $I L B = M g \implies I = \frac{M g}{L B} = \frac{0.5 \times 9.8}{1.0 \times 0.49} = \frac{4.9}{0.49} = 10.0\text{ A}$।</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 35</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>প্রয়োজনীয় প্রবাহ $I = 10.0\text{ A}$</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5488,12 +5215,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>তড়িৎবাহী কুণ্ডলীর ওপর প্রযুক্ত টর্ক (সমস্যা 36)</t>
+          <t>উন্নত চৌম্বক বর্তনী ও কুণ্ডলী বিশ্লেষণ (Advanced Magnetic Circuits)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -5501,25 +5228,25 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[সমস্যা 36: তড়িৎবাহী কুণ্ডলীর ওপর প্রযুক্ত টর্ক]
-একটি $N = 20$ পাকের আয়তাকার কুণ্ডলীর দৈর্ঘ্য $10\text{ cm}$ ও প্রস্থ $5\text{ cm}$। কুণ্ডলীটির মধ্য দিয়ে $I = 2\text{ A}$ প্রবাহ চলছে এবং এটি $B = 0.4\text{ T}$ চৌম্বক ক্ষেত্রের সাথে সমান্তরালে স্থাপিত। কুণ্ডলীটির ওপর প্রযুক্ত টর্ক $\tau = NIAB$ কত?</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি বৃত্তাকার পরিবাহী লুপের ব্যাসার্ধ $R$ এবং তড়িৎ প্রবাহ $I$। লুপটিকে গলিয়ে একই তার দিয়ে দ্বিগুণ ব্যাসার্ধের ($2R$) একটি বৃত্তাকার লুপ তৈরি করে একই প্রবাহ $I$ পাঠালে চৌম্বক ভ্রামকের কী পরিবর্তন ঘটবে?</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 36)।</t>
+          <t>তারের মোট দৈর্ঘ্য $L = 2\pi R \times N_1$। ব্যাসার্ধ দ্বিগুণ হলে পাকসংখ্যা অর্ধেক হয়ে যায়: $N_2 = N_1/2$। নতুন ক্ষেত্রফল $A_2 = \pi (2R)^2 = 4 A_1$। নতুন চৌম্বক ভ্রামক $M_2 = N_2 I A_2 = (N_1/2) I (4 A_1) = 2 N_1 I A_1 = 2 M_1$ (চৌম্বক ভ্রামক দ্বিগুণ বৃদ্ধি পায়)।</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 36</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>চৌম্বক ভ্রামক দ্বিগুণ ($2.0$ গুণ) হবে</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5539,38 +5266,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>সাইক্লোট্রন কম্পাঙ্ক ও পর্যায়কাল (সমস্যা 37)</t>
+          <t>উন্নত চৌম্বক বর্তনী ও কুণ্ডলী বিশ্লেষণ (Advanced Magnetic Circuits)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[সমস্যা 37: সাইক্লোট্রন কম্পাঙ্ক ও পর্যায়কাল]
-$B = 4.0\text{ T}$ চৌম্বক ক্ষেত্রে একটি ইলেকট্রন বৃত্তাকার কক্ষপথে আবর্তন করছে। ইলেকট্রনটির সাইক্লোট্রন কম্পাঙ্ক ($f = \frac{qB}{2\pi m}$) কত মেগাহার্টজ (MHz) হবে?</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##
+একটি দীর্ঘ ফাঁপা নলের অন্তর্ব্যাসার্ধ $a$ এবং বহির্ব্যাসার্ধ $b$। নলের মধ্য দিয়ে সুষমভাবে মোট $I$ প্রবাহ অক্ষ বরাবর চলছে। অ্যাম্পিয়ারের সূত্র প্রয়োগ করে নলের উপাদানের ভেতর ($a &lt; r &lt; b$) চৌম্বক ক্ষেত্রের সমীকরণ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 37)।</t>
+          <t>প্রস্থচ্ছেদের ক্ষেত্রফল $A = \pi(b^2 - a^2)$। কারেন্ট ঘনত্ব $J = \frac{I}{\pi(b^2 - a^2)}$। $r$ ব্যাসার্ধের অ্যাম্পিয়ারিয়ান লুপে আবদ্ধ প্রবাহ $I_{\text{enc}} = J \times \pi(r^2 - a^2) = I \frac{r^2 - a^2}{b^2 - a^2}$। অ্যাম্পিয়ারের সূত্র: $B(2\pi r) = \mu_0 I_{\text{enc}} \implies B = \frac{\mu_0 I}{2\pi r}\frac{r^2 - a^2}{b^2 - a^2}$।</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 37</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>$B(r) = \frac{\mu_0 I}{2\pi r}\left(\frac{r^2 - a^2}{b^2 - a^2}\right)$</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5590,12 +5317,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ভূ-চৌম্বকত্বের আনুভূমিক উপাংশ ও বিনতি কোণ (সমস্যা 38)</t>
+          <t>উন্নত চৌম্বক বর্তনী ও কুণ্ডলী বিশ্লেষণ (Advanced Magnetic Circuits)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -5603,25 +5330,25 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[সমস্যা 38: ভূ-চৌম্বকত্বের আনুভূমিক উপাংশ ও বিনতি কোণ]
-কোনো স্থানে পৃথিবীর মোট চৌম্বক ক্ষেত্রের মান $B = 4 \times 10^{-5}\text{ T}$ এবং বিনতি কোণ $\delta = 60^\circ$। ঐ স্থানে ভূ-চৌম্বক ক্ষেত্রের আনুভূমিক উপাংশ ($B_H = B\cos\delta$) এবং উলম্ব উপাংশ ($B_V$) কত?</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি চৌম্বক দ্বিমেরুর স্থিতিশক্তি $U = -ec{M}\cdotec{B}$। একটি দ্বিমেরুকে সুষম ক্ষেত্রে $	heta = 0^\circ$ (স্থায়ী সাম্যাবস্থা) হতে $	heta = 90^\circ$ কোণে ঘোরাতে কত কাজ করতে হবে এবং $	heta = 180^\circ$ পর্যন্ত ঘোরাতে কৃতকাজ কত?</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 38)।</t>
+          <t>কৃতকাজ $W = \Delta U = -M B(\cos\theta - \cos 0^\circ) = M B(1 - \cos\theta)$। $\theta = 90^\circ$-তে: $W = MB(1 - 0) = MB$। $\theta = 180^\circ$-তে: $W = MB(1 - (-1)) = 2MB$।</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 38</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>$90^\circ$-তে কাজ $W = M B$, $180^\circ$-তে কাজ $W = 2 M B$</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5641,38 +5368,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>অ্যাম্পিয়ারের চক্রীয় সূত্র ও টরয়েড (সমস্যা 39)</t>
+          <t>উন্নত চৌম্বক বর্তনী ও কুণ্ডলী বিশ্লেষণ (Advanced Magnetic Circuits)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[সমস্যা 39: অ্যাম্পিয়ারের চক্রীয় সূত্র ও টরয়েড]
-একটি টরয়েডের গড় ব্যাসার্ধ $R = 80\text{ cm}$ এবং মোট পাকসংখ্যা $N = 13000$। এর মধ্য দিয়ে $I = 3\text{ A}$ তড়িৎ প্রবাহিত হলে টরয়েডের অভ্যন্তরে চৌম্বক ক্ষেত্রের মান কত?</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি অতিপরিবাহী (Superconductor) বস্তুকে চৌম্বক ক্ষেত্রে রাখলে এর অভ্যন্তরীণ চৌম্বক ক্ষেত্র সম্পূর্ণ শূন্য হয়ে যায় (মেইসনার প্রভাব / Meissner Effect)। অতিপরিবাহীর আপেক্ষিক প্রবেশ্যতা $\mu_r$ এবং চৌম্বক গ্রাহিতা $\chi_m$ কত?</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 39)।</t>
+          <t>মেইসনার প্রভাব অনুসারে অতিপরিবাহীর অভ্যন্তরে $\vec{B} = 0 \implies \mu_0(\vec{H} + \vec{M}) = 0 \implies \vec{M} = -\vec{H}$। ফলে চৌম্বক গ্রাহিতা $\chi_m = \frac{M}{H} = -1.0$। আপেক্ষিক প্রবেশ্যতা $\mu_r = 1 + \chi_m = 1 - 1 = 0$। অতিপরিবাহী হলো আদর্শ নিখুঁত ডায়াচৌম্বক।</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 39</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>$\mu_r = 0$, চৌম্বক গ্রাহিতা $\chi_m = -1.0$ (নিখুঁত ডায়াচৌম্বক)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5692,12 +5419,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>চৌম্বক ভ্রামক ও পরমাণুর বোর ম্যাগনেটন (সমস্যা 40)</t>
+          <t>উন্নত চৌম্বক বর্তনী ও কুণ্ডলী বিশ্লেষণ (Advanced Magnetic Circuits)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -5705,25 +5432,25 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[সমস্যা 40: চৌম্বক ভ্রামক ও পরমাণুর বোর ম্যাগনেটন]
-একটি বৃত্তাকার হাইড্রোজেন কক্ষপথে ইলেকট্রন প্রতি সেকেন্ডে $f = 10 \times 10^{15}$ বার ঘোরে। কক্ষপথের ব্যাসার্ধ $r = 0.53\text{ \AA}$ হলে এর সমতুল্য চৌম্বক দ্বিমেরু ভ্রামক ($M = I A$) কত?</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+দুটি সমকেন্দ্রিক বৃত্তাকার কুণ্ডলী পরস্পরের সাথে সমকোণে ($90^\circ$) অবস্থিত। ১ম কুণ্ডলীর ব্যাসার্ধ $R$ ও প্রবাহ $I$, এবং ২য় কুণ্ডলীর ব্যাসার্ধ $R$ ও প্রবাহ $I$। কুণ্ডলীদ্বয়ের সাধারণ কেন্দ্রে লব্ধি চৌম্বক ক্ষেত্র কত?</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 40)।</t>
+          <t>১ম কুণ্ডলীর ক্ষেত্র $B_1 = \frac{\mu_0 I}{2R}$ ($z$-অক্ষে) এবং ২য় কুণ্ডলীর ক্ষেত্র $B_2 = \frac{\mu_0 I}{2R}$ ($x$-অক্ষে)। যেহেতু তলদ্বয় পরস্পরের ওপর লম্ব, তাই চৌম্বক ক্ষেত্র ভেক্টরদ্বয়ও পরস্পরের ওপর লম্ব। লব্ধি $B_{\text{net}} = \sqrt{B_1^2 + B_2^2} = \sqrt{B^2 + B^2} = \sqrt{2} B = \sqrt{2}\frac{\mu_0 I}{2R}$।</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 40</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>লব্ধি চৌম্বক ক্ষেত্র $B_{\text{net}} = \sqrt{2} \frac{\mu_0 I}{2R}$</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5743,44 +5470,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>বৃত্তাকার কুণ্ডলীর কেন্দ্রে চৌম্বক ক্ষেত্র (সমস্যা 41)</t>
+          <t>উন্নত তাত্ত্বিক চুম্বকত্ব ও লব্ধি বিশ্লেষণ (Advanced Magnetism Synthesis)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>##PRESET:solenoid[size:medium]##
-[সমস্যা 41: বৃত্তাকার কুণ্ডলীর কেন্দ্রে চৌম্বক ক্ষেত্র]
-##PRESET:solenoid[size:medium]##
-$N = 1200$ পাকসংখ্যা এবং $R = 4\text{ cm}$ ব্যাসার্ধবিশিষ্ট একটি সমতল বৃত্তাকার তারকুণ্ডলীতে $I = 2.5\text{ A}$ বিদ্যুৎ প্রবাহিত হচ্ছে। কুণ্ডলীর কেন্দ্রে চৌম্বক ক্ষেত্রের মান কত? ($\mu_0 = 4\pi \times 10^{-7}\text{ T}\cdot\text{m/A}$)</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি আয়তাকার কুণ্ডলী $a 	imes b$ একটি সুষম চৌম্বক ক্ষেত্র $B$-এ ধ্রুব কৌণিক দ্রুতি $\omega$-তে আবর্তিত হচ্ছে। কুণ্ডলীতে আবিষ্ট তড়িচ্চালক বলের সর্বোচ্চ মান $\mathcal{E}_0$ এবং কুণ্ডলীর গড় ক্ষমতা নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>##PRESET:solenoid[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 41)।</t>
+          <t>ফ্লাক্স $\Phi(t) = B A \cos(\omega t)$। ফ্যারাডের সূত্রানুযায়ী আবিষ্ট EMF $\mathcal{E} = -\frac{d\Phi}{dt} = N B A \omega \sin(\omega t) = \mathcal{E}_0 \sin(\omega t)$। শীর্ষ মান $\mathcal{E}_0 = N B A \omega$। গড় ক্ষমতা $P = \frac{\mathcal{E}_{\text{rms}}^2}{R} = \frac{\mathcal{E}_0^2}{2R} = \frac{(N B A \omega)^2}{2R}$।</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 41</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>$\mathcal{E}_0 = N B a b \omega$, গড় ক্ষমতা $P_{\text{avg}} = \frac{(N B a b \omega)^2}{2 R}$</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5800,12 +5521,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>দীর্ঘ ঋজু পরিবাহী ও বায়োট-স্যাভার্ট সূত্র (সমস্যা 42)</t>
+          <t>উন্নত তাত্ত্বিক চুম্বকত্ব ও লব্ধি বিশ্লেষণ (Advanced Magnetism Synthesis)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -5813,31 +5534,25 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>##PRESET:magnetic-field-wire[size:medium]##
-[সমস্যা 42: দীর্ঘ ঋজু পরিবাহী ও বায়োট-স্যাভার্ট সূত্র]
-##PRESET:magnetic-field-wire[size:medium]##
-একটি সোজা দীর্ঘ পরিবাহী তারের মধ্য দিয়ে $I = 20\text{ A}$ তড়িৎ প্রবাহিত হচ্ছে। তারটি হতে $d = 7\text{ cm}$ লম্ব দূরত্বে চৌম্বক ক্ষেত্রের মান কত টেসলা?</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি দীর্ঘ সোজা তারের পাশে একই তলে একটি $L$ বাহুবিশিষ্ট বর্গাকার পরিবাহী লুপ রাখা আছে যার নিকটবর্তী বাহু তার হতে $r$ দূরত্বে অবস্থিত। লুপের মধ্য দিয়ে মোট চৌম্বক ফ্লাক্সের সমীকরণ প্রতিপাদন কর।</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>##PRESET:magnetic-field-wire[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 42)।</t>
+          <t>তার হতে $x$ দূরত্বে সরু ফিতার ক্ষেত্রফল $dA = L dx$। চৌম্বক ক্ষেত্র $B(x) = \frac{\mu_0 I}{2\pi x}$। মোট ফ্লাক্স $\Phi = \int_{r}^{r+L} B(x) dA = \int_{r}^{r+L} \frac{\mu_0 I L}{2\pi x} dx = \frac{\mu_0 I L}{2\pi}\ln\left(\frac{r+L}{r}\right)$।</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 42</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>$\Phi = \frac{\mu_0 I L}{2\pi}\ln\left(\frac{r + L}{r}\right)$</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5857,38 +5572,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>চৌম্বক ক্ষেত্রে গতিশীল আধানের ওপর লরেন্টজ বল (সমস্যা 43)</t>
+          <t>উন্নত তাত্ত্বিক চুম্বকত্ব ও লব্ধি বিশ্লেষণ (Advanced Magnetism Synthesis)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[সমস্যা 43: চৌম্বক ক্ষেত্রে গতিশীল আধানের ওপর লরেন্টজ বল]
-একটি প্রোটন ($q = 1.6 \times 10^{-19}\text{ C}$) $B = 0.4\text{ T}$ সুষম চৌম্বক ক্ষেত্রের সাথে লম্বভাবে $v = 10 \times 10^6\text{ m/s}$ বেগে প্রবেশ করল। প্রোটনটির ওপর ক্রিয়াশীল বল এবং এর বৃত্তাকার কক্ষপথের ব্যাসার্ধ কত? ($m = 1.67 \times 10^{-27}\text{ kg}$)</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ইলেকট্রন ও একটি পজিট্রন পরস্পরের দিকে সমান বেগে গতিশীল। তাদের মধ্যকার তড়িৎ বিকর্ষণ এবং চৌম্বক আকর্ষণের অনুপাত $F_e/F_m$ আলোর বেগের সাথে কীভাবে সম্পর্কিত?</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 43)।</t>
+          <t>কুলম্ব বল $F_e = \frac{1}{4\pi\epsilon_0}\frac{q^2}{r^2}$। চৌম্বক বল $F_m = \frac{\mu_0}{4\pi}\frac{q^2 v^2}{r^2}$। অনুপাত $\frac{F_m}{F_e} = \mu_0\epsilon_0 v^2 = \frac{v^2}{c^2}$ কারণ $c = \frac{1}{\sqrt{\mu_0\epsilon_0}}$। সাধারণ নিম্ন বেগে চৌম্বক বল তড়িৎ বলের তুলনায় সম্পূর্ণ নগণ্য।</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 43</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>$\frac{F_m}{F_e} = \frac{v^2}{c^2}$</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5908,12 +5623,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>সোলেনয়েডের অক্ষীয় চৌম্বক প্রাবল্য (সমস্যা 44)</t>
+          <t>উন্নত তাত্ত্বিক চুম্বকত্ব ও লব্ধি বিশ্লেষণ (Advanced Magnetism Synthesis)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -5921,25 +5636,25 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[সমস্যা 44: সোলেনয়েডের অক্ষীয় চৌম্বক প্রাবল্য]
-$L = 0.6\text{ m}$ দীর্ঘ এবং $N = 1300$ পাকবিশিষ্ট একটি সোলেনয়েডের মধ্য দিয়ে $I = 4.0\text{ A}$ প্রবাহ চালনা করা হলে সোলেনয়েডের অভ্যন্তরে অক্ষীয় চৌম্বক আবেশ $B = \mu_0 n I$ কত টেসলা হবে?</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি টরয়েডের ভেতরের ফাঁকা অংশে বাতাস থাকলে $B = 0.01\text{ T}$। টরয়েডের ভেতর লোহার কোর প্রবেশ করালে $B$ বেড়ে $15.0\text{ T}$ হয়। লোহার কোরের আপেক্ষিক প্রবেশ্যতা $\mu_r$ কত?</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 44)।</t>
+          <t>চৌম্বক ক্ষেত্র $B = \mu_r B_0 \implies \mu_r = \frac{B}{B_0} = \frac{15.0\text{ T}}{0.01\text{ T}} = 1500.0$।</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 44</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>আপেক্ষিক প্রবেশ্যতা $\mu_r = 1500.0$</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5959,38 +5674,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>সমান্তরাল পরিবাহী তারদ্বয়ের পারস্পরিক বল (সমস্যা 45)</t>
+          <t>উন্নত তাত্ত্বিক চুম্বকত্ব ও লব্ধি বিশ্লেষণ (Advanced Magnetism Synthesis)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[সমস্যা 45: সমান্তরাল পরিবাহী তারদ্বয়ের পারস্পরিক বল]
-পরস্পর হতে $d = 8\text{ cm}$ দূরত্বে অবস্থিত দুটি সমান্তরাল পরিবাহী তারের মধ্য দিয়ে যথাক্রমে $I_1 = 1\text{ A}$ এবং $I_2 = 15\text{ A}$ বিদ্যুৎ একই দিকে প্রবাহিত হচ্ছে। তার দুটির প্রতি মিটার দৈর্ঘ্যে আকর্ষণ বলের মান কত?</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=1.5][size:small]##
+একটি চুম্বকের দৈর্ঘ্য $2l$, চৌম্বক ভ্রামক $M$ এবং মেরু শক্তি $m$। চুম্বকটিকে (ক) দৈর্ঘ্য বরাবর কেটে সমান দুই ভাগে এবং (খ) দৈর্ঘ্যের লম্ব সমদ্বিখণ্ডক বরাবর কেটে সমান দুই ভাগে ভাগ করলে প্রতিটি অংশের চৌম্বক ভ্রামক ও মেরু শক্তি কী হবে?</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 45)।</t>
+          <t>(ক) দৈর্ঘ্য বরাবর কাটলে মেরু প্রস্থচ্ছেদ অর্ধেক হয়, তাই মেরু শক্তি অর্ধেক $m' = m/2$, দৈর্ঘ্য $2l$ অপরিবর্তিত থাকায় $M' = (m/2)(2l) = M/2$। (খ) লম্ব বরাবর কাটলে দৈর্ঘ্য অর্ধেক হয় ($l' = l$), কিন্তু মেরু শক্তি $m$ অপরিবর্তিত থাকে, ফলে $M' = m(l) = M/2$। উভয় ক্ষেত্রেই প্রতিটি টুকরার চৌম্বক ভ্রামক অর্ধেক হয়।</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 45</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>(ক) দৈর্ঘ্য বরাবর: $m' = m/2, M' = M/2$; (খ) লম্ব বরাবর: $m' = m, M' = M/2$</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6010,12 +5725,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>তড়িৎবাহী কুণ্ডলীর ওপর প্রযুক্ত টর্ক (সমস্যা 46)</t>
+          <t>উন্নত তাত্ত্বিক চুম্বকত্ব ও লব্ধি বিশ্লেষণ (Advanced Magnetism Synthesis)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -6023,25 +5738,25 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[সমস্যা 46: তড়িৎবাহী কুণ্ডলীর ওপর প্রযুক্ত টর্ক]
-একটি $N = 100$ পাকের আয়তাকার কুণ্ডলীর দৈর্ঘ্য $10\text{ cm}$ ও প্রস্থ $5\text{ cm}$। কুণ্ডলীটির মধ্য দিয়ে $I = 2\text{ A}$ প্রবাহ চলছে এবং এটি $B = 0.4\text{ T}$ চৌম্বক ক্ষেত্রের সাথে সমান্তরালে স্থাপিত। কুণ্ডলীটির ওপর প্রযুক্ত টর্ক $\tau = NIAB$ কত?</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি বৃত্তাকার আর্কে আধান $Q$ সুষমভাবে বণ্টিত এবং এটি $\omega$ কৌণিক বেগে নিজ অক্ষের সাপেক্ষে ঘুরছে। উৎপন্ন সমতুল্য কারেন্ট এবং চৌম্বক ভ্রামক নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 46)।</t>
+          <t>পর্যায়কাল $T = \frac{2\pi}{\omega}$। সমতুল্য কারেন্ট $I = \frac{Q}{T} = \frac{Q\omega}{2\pi}$। ক্ষেত্রফল $A = \pi R^2$। চৌম্বক ভ্রামক $M = I A = \left(\frac{Q\omega}{2\pi}\right)(\pi R^2) = \frac{1}{2}Q \omega R^2$।</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 46</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>সমতুল্য কারেন্ট $I = \frac{Q\omega}{2\pi}$, চৌম্বক ভ্রামক $M = \frac{1}{2}Q \omega R^2$</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6061,38 +5776,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>সাইক্লোট্রন কম্পাঙ্ক ও পর্যায়কাল (সমস্যা 47)</t>
+          <t>উন্নত তাত্ত্বিক চুম্বকত্ব ও লব্ধি বিশ্লেষণ (Advanced Magnetism Synthesis)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[সমস্যা 47: সাইক্লোট্রন কম্পাঙ্ক ও পর্যায়কাল]
-$B = 12.0\text{ T}$ চৌম্বক ক্ষেত্রে একটি ইলেকট্রন বৃত্তাকার কক্ষপথে আবর্তন করছে। ইলেকট্রনটির সাইক্লোট্রন কম্পাঙ্ক ($f = \frac{qB}{2\pi m}$) কত মেগাহার্টজ (MHz) হবে?</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি চলকুণ্ডলী গ্যালভানোমিটারের ভোল্টেজ সংবেদনশীলতা $S_v$ এবং কারেন্ট সংবেদনশীলতা $S_i$-এর মধ্যকার সম্পর্ক $S_v = rac{S_i}{R_g}$ প্রমাণ কর। পাকসংখ্যা দ্বিগুণ করলে $S_i$ ও $S_v$-এর কী পরিবর্তন হবে?</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 47)।</t>
+          <t>$S_i = \frac{\theta}{I} = \frac{NAB}{C}$ এবং $S_v = \frac{\theta}{V} = \frac{\theta}{I R_g} = \frac{S_i}{R_g}$। পাকসংখ্যা $N$ দ্বিগুণ করলে কুণ্ডলীর তারের দৈর্ঘ্য দ্বিগুণ হওয়ায় রোধ $R_g$-ও দ্বিগুণ হয়। ফলে $S_i$ দ্বিগুণ হলেও $S_v = \frac{2S_i}{2R_g}$ অপরিবর্তিত থাকে।</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 47</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>$S_i$ দ্বিগুণ হবে, কিন্তু $S_v$ অপরিবর্তিত থাকবে</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6112,12 +5827,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ভূ-চৌম্বকত্বের আনুভূমিক উপাংশ ও বিনতি কোণ (সমস্যা 48)</t>
+          <t>উন্নত তাত্ত্বিক চুম্বকত্ব ও লব্ধি বিশ্লেষণ (Advanced Magnetism Synthesis)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -6125,25 +5840,25 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[সমস্যা 48: ভূ-চৌম্বকত্বের আনুভূমিক উপাংশ ও বিনতি কোণ]
-কোনো স্থানে পৃথিবীর মোট চৌম্বক ক্ষেত্রের মান $B = 4 \times 10^{-5}\text{ T}$ এবং বিনতি কোণ $\delta = 20^\circ$। ঐ স্থানে ভূ-চৌম্বক ক্ষেত্রের আনুভূমিক উপাংশ ($B_H = B\cos\delta$) এবং উলম্ব উপাংশ ($B_V$) কত?</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি সমবাহু ষড়ভুজাকার তারের লুপের কেন্দ্র হতে পরিধির প্রতিটি শীর্ষের দূরত্ব $a$ এবং এতে প্রবাহ $I$। ষড়ভুজের কেন্দ্রে লব্ধি চৌম্বক ক্ষেত্র কত?</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 48)।</t>
+          <t>ষড়ভুজের প্রতিটি বাহুর দৈর্ঘ্য $a$। কেন্দ্র হতে বাহুর লম্ব দূরত্ব $r = a\cos 30^\circ = \frac{\sqrt{3}}{2}a$। প্রান্তদ্বয়ের কোণ $\theta_1 = \theta_2 = 30^\circ$। ১টি বাহুর অবদান $B_1 = \frac{\mu_0 I}{4\pi r}(\sin 30^\circ + \sin 30^\circ) = \frac{\mu_0 I}{4\pi (\frac{\sqrt{3}}{2}a)}(1) = \frac{\mu_0 I}{2\sqrt{3}\pi a}$। ৬টি বাহুর মোট ক্ষেত্র $B = 6 B_1 = 6 \times \frac{\mu_0 I}{2\sqrt{3}\pi a} = \frac{\sqrt{3}\mu_0 I}{\pi a}$।</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 48</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>$B = \frac{\sqrt{3}\mu_0 I}{\pi a}$</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6163,38 +5878,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>অ্যাম্পিয়ারের চক্রীয় সূত্র ও টরয়েড (সমস্যা 49)</t>
+          <t>উন্নত তাত্ত্বিক চুম্বকত্ব ও লব্ধি বিশ্লেষণ (Advanced Magnetism Synthesis)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[সমস্যা 49: অ্যাম্পিয়ারের চক্রীয় সূত্র ও টরয়েড]
-একটি টরয়েডের গড় ব্যাসার্ধ $R = 40\text{ cm}$ এবং মোট পাকসংখ্যা $N = 13000$। এর মধ্য দিয়ে $I = 3\text{ A}$ তড়িৎ প্রবাহিত হলে টরয়েডের অভ্যন্তরে চৌম্বক ক্ষেত্রের মান কত?</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+বায়ো-সাভার্ট সূত্র এবং কুলম্বের সূত্রের মধ্যকার সাদৃশ্য ও বৈসাদৃশ্য ব্যাখ্যা কর।</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 49)।</t>
+          <t>সাদৃশ্য: উভয় ক্ষেত্রই দূরত্বের বর্গের ব্যস্তানুপাতিক ($1/r^2$) এবং উপরিপাতন নীতি মেনে চলে। বৈসাদৃশ্য: কুলম্ব ক্ষেত্র স্কেলার আধান $dq$ দ্বারা সৃষ্ট এবং উৎস ও পর্যবেক্ষণ বিন্দুর সংযোগ রেখা বরাবর (কেন্দ্রীয় বল); কিন্তু চৌম্বক ক্ষেত্র কারেন্ট উপাদান ভেক্টর $I d\vec{l}$ দ্বারা সৃষ্ট এবং সংযোগ তল ও দূরত্বের উভয়ের ওপর লম্ব (ভেক্টর গুণন $\vec{dl} \times \hat{r}$, অ-কেন্দ্রীয় বল)।</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 49</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>উভয়েই ব্যস্ত বর্গীয় সূত্র; তবে কুলম্ব বল কেন্দ্রীয় ও স্কেলার উৎসজাত, বায়ো-সাভার্ট বল অ-কেন্দ্রীয় ও ভেক্টর উৎসজাত</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6214,12 +5929,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>চৌম্বক ভ্রামক ও পরমাণুর বোর ম্যাগনেটন (সমস্যা 50)</t>
+          <t>উন্নত তাত্ত্বিক চুম্বকত্ব ও লব্ধি বিশ্লেষণ (Advanced Magnetism Synthesis)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -6227,25 +5942,25 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[সমস্যা 50: চৌম্বক ভ্রামক ও পরমাণুর বোর ম্যাগনেটন]
-একটি বৃত্তাকার হাইড্রোজেন কক্ষপথে ইলেকট্রন প্রতি সেকেন্ডে $f = 6 \times 10^{15}$ বার ঘোরে। কক্ষপথের ব্যাসার্ধ $r = 0.53\text{ \AA}$ হলে এর সমতুল্য চৌম্বক দ্বিমেরু ভ্রামক ($M = I A$) কত?</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+গাউসের চৌম্বক সূত্র $\oint ec{B}\cdot dec{A} = 0$ বলতে কী বোঝায় এবং এর মৌলিক ভৌত তাৎপর্য কী?</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>বায়োট-স্যাভার্ট সূত্র, অ্যাম্পিয়ারের নিয়ম ও লরেন্টজ চৌম্বক বল সমীকরণ প্রয়োগ করে ধাপে ধাপে নির্ণয় (সমস্যা 50)।</t>
+          <t>যেকোনো বদ্ধ পৃষ্ঠের মধ্য দিয়ে নির্গত নিট চৌম্বক ফ্লাক্স সর্বদা শূন্য। এর অর্থ হলো যেকোনো বদ্ধ পৃষ্ঠে যতগুলো চৌম্বক বলরেখা প্রবেশ করে ঠিক ততগুলোই নির্গত হয়; কোনো চৌম্বক বলরেখার উৎস বা নিঃশেষক বিন্দু আধানের মতো একক চৌম্বক মেরু বাস্তবে প্রকৃতিতে পাওয়া যায় না। চুম্বক সর্বদা উত্তর-দক্ষিণ যুগ্ম মেরুতে অবস্থান করে।</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>চৌম্বক বলবিদ্যার উত্তর 50</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>প্রকৃতিতে কোনো বিচ্ছিন্ন চৌম্বক একক মেরুর (Magnetic monopole) অস্তিত্ব নেই</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
